--- a/output/Primary Analysis Output 2026.xlsx
+++ b/output/Primary Analysis Output 2026.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t xml:space="preserve">Note</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">Addtl</t>
   </si>
   <si>
-    <t xml:space="preserve">All analyses are the proportion of votes to Amy Klobuchar or Peggy Flanagan respectively</t>
+    <t xml:space="preserve">All analyses are the proportion (or ratio) of votes to Amy Klobuchar or Peggy Flanagan respectively. A negative ratio indicates that Amy/Peggy had fewer votes.</t>
   </si>
   <si>
     <t xml:space="preserve">Gov-AmyVRep_St</t>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t xml:space="preserve">prop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratio</t>
   </si>
   <si>
     <t xml:space="preserve">cnty_nme</t>
@@ -1098,21 +1101,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B2" t="n">
         <v>17</v>
@@ -1121,12 +1127,15 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>0.808988764044944</v>
+        <v>0.81</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" t="n">
         <v>402</v>
@@ -1135,12 +1144,15 @@
         <v>868</v>
       </c>
       <c r="D3" t="n">
-        <v>0.683464566929134</v>
+        <v>0.68</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B4" t="n">
         <v>79</v>
@@ -1149,12 +1161,15 @@
         <v>283</v>
       </c>
       <c r="D4" t="n">
-        <v>0.781767955801105</v>
+        <v>0.78</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" t="n">
         <v>77</v>
@@ -1163,12 +1178,15 @@
         <v>325</v>
       </c>
       <c r="D5" t="n">
-        <v>0.808457711442786</v>
+        <v>0.81</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" t="n">
         <v>71</v>
@@ -1177,12 +1195,15 @@
         <v>273</v>
       </c>
       <c r="D6" t="n">
-        <v>0.793604651162791</v>
+        <v>0.79</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="n">
         <v>71</v>
@@ -1191,12 +1212,15 @@
         <v>298</v>
       </c>
       <c r="D7" t="n">
-        <v>0.807588075880759</v>
+        <v>0.81</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="n">
         <v>300</v>
@@ -1205,12 +1229,15 @@
         <v>864</v>
       </c>
       <c r="D8" t="n">
-        <v>0.742268041237113</v>
+        <v>0.74</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" t="n">
         <v>115</v>
@@ -1219,12 +1246,15 @@
         <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>0.765784114052953</v>
+        <v>0.77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="n">
         <v>56</v>
@@ -1233,12 +1263,15 @@
         <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>0.769547325102881</v>
+        <v>0.77</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11" t="n">
         <v>327</v>
@@ -1247,12 +1280,15 @@
         <v>912</v>
       </c>
       <c r="D11" t="n">
-        <v>0.736077481840194</v>
+        <v>0.74</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" t="n">
         <v>65</v>
@@ -1261,12 +1297,15 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>0.610778443113772</v>
+        <v>0.61</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" t="n">
         <v>45</v>
@@ -1275,12 +1314,15 @@
         <v>195</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8125</v>
+        <v>0.81</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" t="n">
         <v>33</v>
@@ -1291,10 +1333,13 @@
       <c r="D14" t="n">
         <v>0.8</v>
       </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="n">
         <v>226</v>
@@ -1303,12 +1348,15 @@
         <v>505</v>
       </c>
       <c r="D15" t="n">
-        <v>0.690834473324213</v>
+        <v>0.69</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="n">
         <v>157</v>
@@ -1317,12 +1365,15 @@
         <v>490</v>
       </c>
       <c r="D16" t="n">
-        <v>0.757341576506955</v>
+        <v>0.76</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="n">
         <v>92</v>
@@ -1331,12 +1382,15 @@
         <v>277</v>
       </c>
       <c r="D17" t="n">
-        <v>0.750677506775068</v>
+        <v>0.75</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="n">
         <v>161</v>
@@ -1345,12 +1399,15 @@
         <v>563</v>
       </c>
       <c r="D18" t="n">
-        <v>0.777624309392265</v>
+        <v>0.78</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="n">
         <v>385</v>
@@ -1359,12 +1416,15 @@
         <v>800</v>
       </c>
       <c r="D19" t="n">
-        <v>0.675105485232067</v>
+        <v>0.68</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" t="n">
         <v>388</v>
@@ -1373,12 +1433,15 @@
         <v>659</v>
       </c>
       <c r="D20" t="n">
-        <v>0.629417382999045</v>
+        <v>0.63</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B21" t="n">
         <v>270</v>
@@ -1387,12 +1450,15 @@
         <v>732</v>
       </c>
       <c r="D21" t="n">
-        <v>0.730538922155689</v>
+        <v>0.73</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B22" t="n">
         <v>299</v>
@@ -1401,12 +1467,15 @@
         <v>531</v>
       </c>
       <c r="D22" t="n">
-        <v>0.639759036144578</v>
+        <v>0.64</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B23" t="n">
         <v>172</v>
@@ -1415,12 +1484,15 @@
         <v>491</v>
       </c>
       <c r="D23" t="n">
-        <v>0.740573152337858</v>
+        <v>0.74</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B24" t="n">
         <v>79</v>
@@ -1429,12 +1501,15 @@
         <v>265</v>
       </c>
       <c r="D24" t="n">
-        <v>0.770348837209302</v>
+        <v>0.77</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" t="n">
         <v>187</v>
@@ -1443,12 +1518,15 @@
         <v>719</v>
       </c>
       <c r="D25" t="n">
-        <v>0.793598233995585</v>
+        <v>0.79</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B26" t="n">
         <v>89</v>
@@ -1457,12 +1535,15 @@
         <v>415</v>
       </c>
       <c r="D26" t="n">
-        <v>0.823412698412698</v>
+        <v>0.82</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B27" t="n">
         <v>15</v>
@@ -1471,12 +1552,15 @@
         <v>73</v>
       </c>
       <c r="D27" t="n">
-        <v>0.829545454545455</v>
+        <v>0.83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" t="n">
         <v>596</v>
@@ -1485,12 +1569,15 @@
         <v>788</v>
       </c>
       <c r="D28" t="n">
-        <v>0.569364161849711</v>
+        <v>0.57</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B29" t="n">
         <v>575</v>
@@ -1499,12 +1586,15 @@
         <v>1061</v>
       </c>
       <c r="D29" t="n">
-        <v>0.648533007334963</v>
+        <v>0.65</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B30" t="n">
         <v>621</v>
@@ -1513,12 +1603,15 @@
         <v>769</v>
       </c>
       <c r="D30" t="n">
-        <v>0.553237410071942</v>
+        <v>0.55</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B31" t="n">
         <v>632</v>
@@ -1527,12 +1620,15 @@
         <v>778</v>
       </c>
       <c r="D31" t="n">
-        <v>0.55177304964539</v>
+        <v>0.55</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B32" t="n">
         <v>235</v>
@@ -1541,12 +1637,15 @@
         <v>464</v>
       </c>
       <c r="D32" t="n">
-        <v>0.663805436337625</v>
+        <v>0.66</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B33" t="n">
         <v>405</v>
@@ -1555,12 +1654,15 @@
         <v>551</v>
       </c>
       <c r="D33" t="n">
-        <v>0.576359832635983</v>
+        <v>0.58</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B34" t="n">
         <v>176</v>
@@ -1569,12 +1671,15 @@
         <v>394</v>
       </c>
       <c r="D34" t="n">
-        <v>0.691228070175439</v>
+        <v>0.69</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B35" t="n">
         <v>261</v>
@@ -1583,12 +1688,15 @@
         <v>457</v>
       </c>
       <c r="D35" t="n">
-        <v>0.636490250696379</v>
+        <v>0.64</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B36" t="n">
         <v>420</v>
@@ -1597,12 +1705,15 @@
         <v>995</v>
       </c>
       <c r="D36" t="n">
-        <v>0.703180212014134</v>
+        <v>0.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B37" t="n">
         <v>581</v>
@@ -1611,12 +1722,15 @@
         <v>720</v>
       </c>
       <c r="D37" t="n">
-        <v>0.553420445810915</v>
+        <v>0.55</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B38" t="n">
         <v>305</v>
@@ -1625,12 +1739,15 @@
         <v>460</v>
       </c>
       <c r="D38" t="n">
-        <v>0.601307189542484</v>
+        <v>0.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B39" t="n">
         <v>66</v>
@@ -1639,12 +1756,15 @@
         <v>175</v>
       </c>
       <c r="D39" t="n">
-        <v>0.726141078838174</v>
+        <v>0.73</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B40" t="n">
         <v>409</v>
@@ -1653,12 +1773,15 @@
         <v>787</v>
       </c>
       <c r="D40" t="n">
-        <v>0.658026755852843</v>
+        <v>0.66</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" t="n">
         <v>355</v>
@@ -1667,12 +1790,15 @@
         <v>461</v>
       </c>
       <c r="D41" t="n">
-        <v>0.564950980392157</v>
+        <v>0.56</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" t="n">
         <v>227</v>
@@ -1681,12 +1807,15 @@
         <v>569</v>
       </c>
       <c r="D42" t="n">
-        <v>0.714824120603015</v>
+        <v>0.71</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" t="n">
         <v>185</v>
@@ -1695,12 +1824,15 @@
         <v>884</v>
       </c>
       <c r="D43" t="n">
-        <v>0.826941066417212</v>
+        <v>0.83</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" t="n">
         <v>278</v>
@@ -1709,12 +1841,15 @@
         <v>723</v>
       </c>
       <c r="D44" t="n">
-        <v>0.722277722277722</v>
+        <v>0.72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" t="n">
         <v>226</v>
@@ -1723,12 +1858,15 @@
         <v>373</v>
       </c>
       <c r="D45" t="n">
-        <v>0.622704507512521</v>
+        <v>0.62</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" t="n">
         <v>312</v>
@@ -1737,12 +1875,15 @@
         <v>867</v>
       </c>
       <c r="D46" t="n">
-        <v>0.735368956743003</v>
+        <v>0.74</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.78</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" t="n">
         <v>210</v>
@@ -1751,12 +1892,15 @@
         <v>1105</v>
       </c>
       <c r="D47" t="n">
-        <v>0.840304182509506</v>
+        <v>0.84</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" t="n">
         <v>202</v>
@@ -1765,12 +1909,15 @@
         <v>914</v>
       </c>
       <c r="D48" t="n">
-        <v>0.818996415770609</v>
+        <v>0.82</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B49" t="n">
         <v>130</v>
@@ -1779,12 +1926,15 @@
         <v>303</v>
       </c>
       <c r="D49" t="n">
-        <v>0.699769053117783</v>
+        <v>0.7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" t="n">
         <v>91</v>
@@ -1793,12 +1943,15 @@
         <v>482</v>
       </c>
       <c r="D50" t="n">
-        <v>0.841186736474695</v>
+        <v>0.84</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B51" t="n">
         <v>110</v>
@@ -1809,10 +1962,13 @@
       <c r="D51" t="n">
         <v>0.8</v>
       </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" t="n">
         <v>400</v>
@@ -1821,12 +1977,15 @@
         <v>644</v>
       </c>
       <c r="D52" t="n">
-        <v>0.616858237547893</v>
+        <v>0.62</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B53" t="n">
         <v>331</v>
@@ -1835,12 +1994,15 @@
         <v>748</v>
       </c>
       <c r="D53" t="n">
-        <v>0.693234476367007</v>
+        <v>0.69</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.26</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B54" t="n">
         <v>340</v>
@@ -1849,12 +2011,15 @@
         <v>789</v>
       </c>
       <c r="D54" t="n">
-        <v>0.698848538529672</v>
+        <v>0.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B55" t="n">
         <v>165</v>
@@ -1863,12 +2028,15 @@
         <v>414</v>
       </c>
       <c r="D55" t="n">
-        <v>0.715025906735751</v>
+        <v>0.72</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.51</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B56" t="n">
         <v>251</v>
@@ -1877,12 +2045,15 @@
         <v>808</v>
       </c>
       <c r="D56" t="n">
-        <v>0.762983947119924</v>
+        <v>0.76</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B57" t="n">
         <v>206</v>
@@ -1891,12 +2062,15 @@
         <v>553</v>
       </c>
       <c r="D57" t="n">
-        <v>0.728590250329381</v>
+        <v>0.73</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B58" t="n">
         <v>43</v>
@@ -1905,12 +2079,15 @@
         <v>121</v>
       </c>
       <c r="D58" t="n">
-        <v>0.73780487804878</v>
+        <v>0.74</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B59" t="n">
         <v>103</v>
@@ -1919,12 +2096,15 @@
         <v>300</v>
       </c>
       <c r="D59" t="n">
-        <v>0.744416873449132</v>
+        <v>0.74</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B60" t="n">
         <v>124</v>
@@ -1933,12 +2113,15 @@
         <v>314</v>
       </c>
       <c r="D60" t="n">
-        <v>0.71689497716895</v>
+        <v>0.72</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" t="n">
         <v>91</v>
@@ -1947,12 +2130,15 @@
         <v>274</v>
       </c>
       <c r="D61" t="n">
-        <v>0.750684931506849</v>
+        <v>0.75</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.01</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B62" t="n">
         <v>57</v>
@@ -1961,12 +2147,15 @@
         <v>225</v>
       </c>
       <c r="D62" t="n">
-        <v>0.797872340425532</v>
+        <v>0.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3.95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B63" t="n">
         <v>61</v>
@@ -1975,12 +2164,15 @@
         <v>152</v>
       </c>
       <c r="D63" t="n">
-        <v>0.713615023474178</v>
+        <v>0.71</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B64" t="n">
         <v>46</v>
@@ -1989,12 +2181,15 @@
         <v>191</v>
       </c>
       <c r="D64" t="n">
-        <v>0.805907172995781</v>
+        <v>0.81</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4.15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B65" t="n">
         <v>132</v>
@@ -2003,12 +2198,15 @@
         <v>469</v>
       </c>
       <c r="D65" t="n">
-        <v>0.780366056572379</v>
+        <v>0.78</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3.55</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B66" t="n">
         <v>72</v>
@@ -2017,12 +2215,15 @@
         <v>181</v>
       </c>
       <c r="D66" t="n">
-        <v>0.715415019762846</v>
+        <v>0.72</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B67" t="n">
         <v>70</v>
@@ -2031,12 +2232,15 @@
         <v>144</v>
       </c>
       <c r="D67" t="n">
-        <v>0.672897196261682</v>
+        <v>0.67</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B68" t="n">
         <v>79</v>
@@ -2045,12 +2249,15 @@
         <v>249</v>
       </c>
       <c r="D68" t="n">
-        <v>0.759146341463415</v>
+        <v>0.76</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B69" t="n">
         <v>52</v>
@@ -2059,12 +2266,15 @@
         <v>193</v>
       </c>
       <c r="D69" t="n">
-        <v>0.787755102040816</v>
+        <v>0.79</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3.71</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B70" t="n">
         <v>40</v>
@@ -2073,12 +2283,15 @@
         <v>137</v>
       </c>
       <c r="D70" t="n">
-        <v>0.774011299435028</v>
+        <v>0.77</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3.42</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B71" t="n">
         <v>57</v>
@@ -2087,12 +2300,15 @@
         <v>167</v>
       </c>
       <c r="D71" t="n">
-        <v>0.745535714285714</v>
+        <v>0.75</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B72" t="n">
         <v>72</v>
@@ -2101,12 +2317,15 @@
         <v>142</v>
       </c>
       <c r="D72" t="n">
-        <v>0.663551401869159</v>
+        <v>0.66</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B73" t="n">
         <v>84</v>
@@ -2115,12 +2334,15 @@
         <v>225</v>
       </c>
       <c r="D73" t="n">
-        <v>0.728155339805825</v>
+        <v>0.73</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B74" t="n">
         <v>110</v>
@@ -2129,12 +2351,15 @@
         <v>267</v>
       </c>
       <c r="D74" t="n">
-        <v>0.708222811671088</v>
+        <v>0.71</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.43</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B75" t="n">
         <v>61</v>
@@ -2143,12 +2368,15 @@
         <v>260</v>
       </c>
       <c r="D75" t="n">
-        <v>0.809968847352025</v>
+        <v>0.81</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4.26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B76" t="n">
         <v>26</v>
@@ -2157,12 +2385,15 @@
         <v>95</v>
       </c>
       <c r="D76" t="n">
-        <v>0.785123966942149</v>
+        <v>0.79</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B77" t="n">
         <v>53</v>
@@ -2171,12 +2402,15 @@
         <v>205</v>
       </c>
       <c r="D77" t="n">
-        <v>0.794573643410853</v>
+        <v>0.79</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B78" t="n">
         <v>66</v>
@@ -2185,12 +2419,15 @@
         <v>220</v>
       </c>
       <c r="D78" t="n">
-        <v>0.769230769230769</v>
+        <v>0.77</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B79" t="n">
         <v>113</v>
@@ -2199,12 +2436,15 @@
         <v>292</v>
       </c>
       <c r="D79" t="n">
-        <v>0.720987654320988</v>
+        <v>0.72</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.58</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B80" t="n">
         <v>68</v>
@@ -2213,12 +2453,15 @@
         <v>182</v>
       </c>
       <c r="D80" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B81" t="n">
         <v>67</v>
@@ -2227,12 +2470,15 @@
         <v>116</v>
       </c>
       <c r="D81" t="n">
-        <v>0.633879781420765</v>
+        <v>0.63</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B82" t="n">
         <v>134</v>
@@ -2241,12 +2487,15 @@
         <v>244</v>
       </c>
       <c r="D82" t="n">
-        <v>0.645502645502645</v>
+        <v>0.65</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.82</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B83" t="n">
         <v>72</v>
@@ -2255,12 +2504,15 @@
         <v>202</v>
       </c>
       <c r="D83" t="n">
-        <v>0.737226277372263</v>
+        <v>0.74</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B84" t="n">
         <v>70</v>
@@ -2269,12 +2521,15 @@
         <v>240</v>
       </c>
       <c r="D84" t="n">
-        <v>0.774193548387097</v>
+        <v>0.77</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3.43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" t="n">
         <v>38</v>
@@ -2283,12 +2538,15 @@
         <v>139</v>
       </c>
       <c r="D85" t="n">
-        <v>0.785310734463277</v>
+        <v>0.79</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B86" t="n">
         <v>169</v>
@@ -2297,12 +2555,15 @@
         <v>332</v>
       </c>
       <c r="D86" t="n">
-        <v>0.662674650698603</v>
+        <v>0.66</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B87" t="n">
         <v>167</v>
@@ -2311,7 +2572,10 @@
         <v>336</v>
       </c>
       <c r="D87" t="n">
-        <v>0.667992047713718</v>
+        <v>0.67</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.01</v>
       </c>
     </row>
   </sheetData>
@@ -2335,6 +2599,9 @@
       <c r="C1" t="s">
         <v>27</v>
       </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2344,7 +2611,10 @@
         <v>413279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.597829746735667</v>
+        <v>0.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>
@@ -2360,7 +2630,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
         <v>25</v>
@@ -2371,10 +2641,13 @@
       <c r="D1" t="s">
         <v>27</v>
       </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="n">
         <v>1588</v>
@@ -2383,12 +2656,15 @@
         <v>2629</v>
       </c>
       <c r="D2" t="n">
-        <v>0.376571022053593</v>
+        <v>0.38</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="n">
         <v>31324</v>
@@ -2397,12 +2673,15 @@
         <v>28846</v>
       </c>
       <c r="D3" t="n">
-        <v>0.520591656971913</v>
+        <v>0.52</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="n">
         <v>2290</v>
@@ -2411,12 +2690,15 @@
         <v>3797</v>
       </c>
       <c r="D4" t="n">
-        <v>0.376211598488582</v>
+        <v>0.38</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="n">
         <v>3659</v>
@@ -2425,12 +2707,15 @@
         <v>3162</v>
       </c>
       <c r="D5" t="n">
-        <v>0.536431608268582</v>
+        <v>0.54</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="n">
         <v>1904</v>
@@ -2439,12 +2724,15 @@
         <v>4116</v>
       </c>
       <c r="D6" t="n">
-        <v>0.316279069767442</v>
+        <v>0.32</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="n">
         <v>392</v>
@@ -2453,12 +2741,15 @@
         <v>556</v>
       </c>
       <c r="D7" t="n">
-        <v>0.413502109704641</v>
+        <v>0.41</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="n">
         <v>5508</v>
@@ -2467,12 +2758,15 @@
         <v>4076</v>
       </c>
       <c r="D8" t="n">
-        <v>0.574707846410685</v>
+        <v>0.57</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="n">
         <v>1606</v>
@@ -2481,12 +2775,15 @@
         <v>2668</v>
       </c>
       <c r="D9" t="n">
-        <v>0.375760411792232</v>
+        <v>0.38</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="n">
         <v>3892</v>
@@ -2495,12 +2792,15 @@
         <v>2993</v>
       </c>
       <c r="D10" t="n">
-        <v>0.565286855482934</v>
+        <v>0.57</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="n">
         <v>10215</v>
@@ -2509,12 +2809,15 @@
         <v>10290</v>
       </c>
       <c r="D11" t="n">
-        <v>0.498171177761522</v>
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="n">
         <v>2327</v>
@@ -2523,12 +2826,15 @@
         <v>4381</v>
       </c>
       <c r="D12" t="n">
-        <v>0.346899224806202</v>
+        <v>0.35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>724</v>
@@ -2537,12 +2843,15 @@
         <v>1074</v>
       </c>
       <c r="D13" t="n">
-        <v>0.402669632925473</v>
+        <v>0.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="n">
         <v>3944</v>
@@ -2551,12 +2860,15 @@
         <v>5572</v>
       </c>
       <c r="D14" t="n">
-        <v>0.414459857082808</v>
+        <v>0.41</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="n">
         <v>5106</v>
@@ -2565,12 +2877,15 @@
         <v>2821</v>
       </c>
       <c r="D15" t="n">
-        <v>0.644127664942601</v>
+        <v>0.64</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
         <v>496</v>
@@ -2579,12 +2894,15 @@
         <v>1351</v>
       </c>
       <c r="D16" t="n">
-        <v>0.268543584190579</v>
+        <v>0.27</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
         <v>1403</v>
@@ -2593,12 +2911,15 @@
         <v>503</v>
       </c>
       <c r="D17" t="n">
-        <v>0.736096537250787</v>
+        <v>0.74</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="n">
         <v>423</v>
@@ -2607,12 +2928,15 @@
         <v>920</v>
       </c>
       <c r="D18" t="n">
-        <v>0.314966492926284</v>
+        <v>0.31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="n">
         <v>4884</v>
@@ -2621,12 +2945,15 @@
         <v>8070</v>
       </c>
       <c r="D19" t="n">
-        <v>0.377026401111626</v>
+        <v>0.38</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="n">
         <v>55404</v>
@@ -2635,12 +2962,15 @@
         <v>29508</v>
       </c>
       <c r="D20" t="n">
-        <v>0.652487280949689</v>
+        <v>0.65</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" t="n">
         <v>1043</v>
@@ -2649,12 +2979,15 @@
         <v>1868</v>
       </c>
       <c r="D21" t="n">
-        <v>0.358296118172449</v>
+        <v>0.36</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" t="n">
         <v>2895</v>
@@ -2663,12 +2996,15 @@
         <v>4805</v>
       </c>
       <c r="D22" t="n">
-        <v>0.375974025974026</v>
+        <v>0.38</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="n">
         <v>1118</v>
@@ -2677,12 +3013,15 @@
         <v>2337</v>
       </c>
       <c r="D23" t="n">
-        <v>0.323589001447178</v>
+        <v>0.32</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" t="n">
         <v>1537</v>
@@ -2691,12 +3030,15 @@
         <v>1939</v>
       </c>
       <c r="D24" t="n">
-        <v>0.442174913693901</v>
+        <v>0.44</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="n">
         <v>1973</v>
@@ -2705,12 +3047,15 @@
         <v>2397</v>
       </c>
       <c r="D25" t="n">
-        <v>0.451487414187643</v>
+        <v>0.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" t="n">
         <v>4306</v>
@@ -2719,12 +3064,15 @@
         <v>4512</v>
       </c>
       <c r="D26" t="n">
-        <v>0.488319346790655</v>
+        <v>0.49</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" t="n">
         <v>540</v>
@@ -2733,12 +3081,15 @@
         <v>712</v>
       </c>
       <c r="D27" t="n">
-        <v>0.431309904153355</v>
+        <v>0.43</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" t="n">
         <v>204781</v>
@@ -2747,12 +3098,15 @@
         <v>55565</v>
       </c>
       <c r="D28" t="n">
-        <v>0.786572484309342</v>
+        <v>0.79</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" t="n">
         <v>1351</v>
@@ -2761,12 +3115,15 @@
         <v>1516</v>
       </c>
       <c r="D29" t="n">
-        <v>0.471224276246948</v>
+        <v>0.47</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" t="n">
         <v>1749</v>
@@ -2775,12 +3132,15 @@
         <v>2547</v>
       </c>
       <c r="D30" t="n">
-        <v>0.407122905027933</v>
+        <v>0.41</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B31" t="n">
         <v>2492</v>
@@ -2789,12 +3149,15 @@
         <v>5078</v>
       </c>
       <c r="D31" t="n">
-        <v>0.329194187582563</v>
+        <v>0.33</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" t="n">
         <v>4298</v>
@@ -2803,12 +3166,15 @@
         <v>5005</v>
       </c>
       <c r="D32" t="n">
-        <v>0.462001504890895</v>
+        <v>0.46</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" t="n">
         <v>498</v>
@@ -2817,12 +3183,15 @@
         <v>1083</v>
       </c>
       <c r="D33" t="n">
-        <v>0.314990512333966</v>
+        <v>0.31</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B34" t="n">
         <v>914</v>
@@ -2831,12 +3200,15 @@
         <v>1673</v>
       </c>
       <c r="D34" t="n">
-        <v>0.353304986470816</v>
+        <v>0.35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" t="n">
         <v>2807</v>
@@ -2845,12 +3217,15 @@
         <v>4194</v>
       </c>
       <c r="D35" t="n">
-        <v>0.400942722468219</v>
+        <v>0.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36" t="n">
         <v>457</v>
@@ -2859,12 +3234,15 @@
         <v>521</v>
       </c>
       <c r="D36" t="n">
-        <v>0.467280163599182</v>
+        <v>0.47</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B37" t="n">
         <v>1023</v>
@@ -2873,12 +3251,15 @@
         <v>1364</v>
       </c>
       <c r="D37" t="n">
-        <v>0.428571428571429</v>
+        <v>0.43</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B38" t="n">
         <v>505</v>
@@ -2887,12 +3268,15 @@
         <v>760</v>
       </c>
       <c r="D38" t="n">
-        <v>0.399209486166008</v>
+        <v>0.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B39" t="n">
         <v>1602</v>
@@ -2901,12 +3285,15 @@
         <v>1083</v>
       </c>
       <c r="D39" t="n">
-        <v>0.596648044692737</v>
+        <v>0.6</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B40" t="n">
         <v>250</v>
@@ -2915,12 +3302,15 @@
         <v>584</v>
       </c>
       <c r="D40" t="n">
-        <v>0.299760191846523</v>
+        <v>0.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B41" t="n">
         <v>2020</v>
@@ -2929,12 +3319,15 @@
         <v>3245</v>
       </c>
       <c r="D41" t="n">
-        <v>0.38366571699905</v>
+        <v>0.38</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B42" t="n">
         <v>276</v>
@@ -2943,12 +3336,15 @@
         <v>473</v>
       </c>
       <c r="D42" t="n">
-        <v>0.36849132176235</v>
+        <v>0.37</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B43" t="n">
         <v>1301</v>
@@ -2957,12 +3353,15 @@
         <v>2364</v>
       </c>
       <c r="D43" t="n">
-        <v>0.354979536152797</v>
+        <v>0.35</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B44" t="n">
         <v>378</v>
@@ -2971,12 +3370,15 @@
         <v>384</v>
       </c>
       <c r="D44" t="n">
-        <v>0.496062992125984</v>
+        <v>0.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B45" t="n">
         <v>451</v>
@@ -2985,12 +3387,15 @@
         <v>1091</v>
       </c>
       <c r="D45" t="n">
-        <v>0.292477302204929</v>
+        <v>0.29</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B46" t="n">
         <v>883</v>
@@ -2999,12 +3404,15 @@
         <v>1899</v>
       </c>
       <c r="D46" t="n">
-        <v>0.317397555715313</v>
+        <v>0.32</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B47" t="n">
         <v>1698</v>
@@ -3013,12 +3421,15 @@
         <v>3306</v>
       </c>
       <c r="D47" t="n">
-        <v>0.339328537170264</v>
+        <v>0.34</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B48" t="n">
         <v>1204</v>
@@ -3027,12 +3438,15 @@
         <v>2605</v>
       </c>
       <c r="D48" t="n">
-        <v>0.316093462851142</v>
+        <v>0.32</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B49" t="n">
         <v>1281</v>
@@ -3041,12 +3455,15 @@
         <v>2787</v>
       </c>
       <c r="D49" t="n">
-        <v>0.314896755162242</v>
+        <v>0.31</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B50" t="n">
         <v>1375</v>
@@ -3055,12 +3472,15 @@
         <v>5669</v>
       </c>
       <c r="D50" t="n">
-        <v>0.195201590005679</v>
+        <v>0.2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-4.12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B51" t="n">
         <v>2268</v>
@@ -3069,12 +3489,15 @@
         <v>2210</v>
       </c>
       <c r="D51" t="n">
-        <v>0.506476105404198</v>
+        <v>0.51</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B52" t="n">
         <v>452</v>
@@ -3083,12 +3506,15 @@
         <v>1009</v>
       </c>
       <c r="D52" t="n">
-        <v>0.309377138945927</v>
+        <v>0.31</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B53" t="n">
         <v>3070</v>
@@ -3097,12 +3523,15 @@
         <v>2454</v>
       </c>
       <c r="D53" t="n">
-        <v>0.555756698044895</v>
+        <v>0.56</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B54" t="n">
         <v>645</v>
@@ -3111,12 +3540,15 @@
         <v>1359</v>
       </c>
       <c r="D54" t="n">
-        <v>0.32185628742515</v>
+        <v>0.32</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B55" t="n">
         <v>570</v>
@@ -3125,12 +3557,15 @@
         <v>646</v>
       </c>
       <c r="D55" t="n">
-        <v>0.46875</v>
+        <v>0.47</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B56" t="n">
         <v>17444</v>
@@ -3139,12 +3574,15 @@
         <v>12079</v>
       </c>
       <c r="D56" t="n">
-        <v>0.590861362327677</v>
+        <v>0.59</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B57" t="n">
         <v>3825</v>
@@ -3153,12 +3591,15 @@
         <v>6854</v>
       </c>
       <c r="D57" t="n">
-        <v>0.358179604831913</v>
+        <v>0.36</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B58" t="n">
         <v>516</v>
@@ -3167,12 +3608,15 @@
         <v>835</v>
       </c>
       <c r="D58" t="n">
-        <v>0.381939304219097</v>
+        <v>0.38</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B59" t="n">
         <v>1933</v>
@@ -3181,12 +3625,15 @@
         <v>3179</v>
       </c>
       <c r="D59" t="n">
-        <v>0.378129890453834</v>
+        <v>0.38</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B60" t="n">
         <v>478</v>
@@ -3195,12 +3642,15 @@
         <v>1549</v>
       </c>
       <c r="D60" t="n">
-        <v>0.235816477553034</v>
+        <v>0.24</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B61" t="n">
         <v>1482</v>
@@ -3209,12 +3659,15 @@
         <v>2314</v>
       </c>
       <c r="D61" t="n">
-        <v>0.39041095890411</v>
+        <v>0.39</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B62" t="n">
         <v>864</v>
@@ -3223,12 +3676,15 @@
         <v>1298</v>
       </c>
       <c r="D62" t="n">
-        <v>0.399629972247919</v>
+        <v>0.4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B63" t="n">
         <v>78614</v>
@@ -3237,12 +3693,15 @@
         <v>19792</v>
       </c>
       <c r="D63" t="n">
-        <v>0.798874052395179</v>
+        <v>0.8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3.97</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B64" t="n">
         <v>257</v>
@@ -3251,12 +3710,15 @@
         <v>402</v>
       </c>
       <c r="D64" t="n">
-        <v>0.389984825493171</v>
+        <v>0.39</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B65" t="n">
         <v>734</v>
@@ -3265,12 +3727,15 @@
         <v>1580</v>
       </c>
       <c r="D65" t="n">
-        <v>0.317199654278306</v>
+        <v>0.32</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B66" t="n">
         <v>611</v>
@@ -3279,12 +3744,15 @@
         <v>1226</v>
       </c>
       <c r="D66" t="n">
-        <v>0.332607512248231</v>
+        <v>0.33</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B67" t="n">
         <v>6436</v>
@@ -3293,12 +3761,15 @@
         <v>4864</v>
       </c>
       <c r="D67" t="n">
-        <v>0.569557522123894</v>
+        <v>0.57</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B68" t="n">
         <v>561</v>
@@ -3307,12 +3778,15 @@
         <v>1015</v>
       </c>
       <c r="D68" t="n">
-        <v>0.355964467005076</v>
+        <v>0.36</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B69" t="n">
         <v>574</v>
@@ -3321,12 +3795,15 @@
         <v>1524</v>
       </c>
       <c r="D69" t="n">
-        <v>0.273593898951382</v>
+        <v>0.27</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B70" t="n">
         <v>12895</v>
@@ -3335,12 +3812,15 @@
         <v>12412</v>
       </c>
       <c r="D70" t="n">
-        <v>0.509542814241119</v>
+        <v>0.51</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B71" t="n">
         <v>4867</v>
@@ -3349,12 +3829,15 @@
         <v>9223</v>
       </c>
       <c r="D71" t="n">
-        <v>0.34542228530873</v>
+        <v>0.35</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B72" t="n">
         <v>1013</v>
@@ -3363,12 +3846,15 @@
         <v>2217</v>
       </c>
       <c r="D72" t="n">
-        <v>0.313622291021672</v>
+        <v>0.31</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B73" t="n">
         <v>26010</v>
@@ -3377,12 +3863,15 @@
         <v>12640</v>
       </c>
       <c r="D73" t="n">
-        <v>0.672962483829237</v>
+        <v>0.67</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B74" t="n">
         <v>10054</v>
@@ -3391,12 +3880,15 @@
         <v>16323</v>
       </c>
       <c r="D74" t="n">
-        <v>0.381165409258066</v>
+        <v>0.38</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B75" t="n">
         <v>2231</v>
@@ -3405,12 +3897,15 @@
         <v>3189</v>
       </c>
       <c r="D75" t="n">
-        <v>0.411623616236162</v>
+        <v>0.41</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B76" t="n">
         <v>640</v>
@@ -3419,12 +3914,15 @@
         <v>902</v>
       </c>
       <c r="D76" t="n">
-        <v>0.415045395590143</v>
+        <v>0.42</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B77" t="n">
         <v>659</v>
@@ -3433,12 +3931,15 @@
         <v>928</v>
       </c>
       <c r="D77" t="n">
-        <v>0.415248897290485</v>
+        <v>0.42</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B78" t="n">
         <v>1053</v>
@@ -3447,12 +3948,15 @@
         <v>3116</v>
       </c>
       <c r="D78" t="n">
-        <v>0.252578556008635</v>
+        <v>0.25</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B79" t="n">
         <v>192</v>
@@ -3461,12 +3965,15 @@
         <v>371</v>
       </c>
       <c r="D79" t="n">
-        <v>0.341030195381883</v>
+        <v>0.34</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B80" t="n">
         <v>1671</v>
@@ -3475,12 +3982,15 @@
         <v>2331</v>
       </c>
       <c r="D80" t="n">
-        <v>0.417541229385307</v>
+        <v>0.42</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B81" t="n">
         <v>735</v>
@@ -3489,12 +3999,15 @@
         <v>2255</v>
       </c>
       <c r="D81" t="n">
-        <v>0.245819397993311</v>
+        <v>0.25</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-3.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B82" t="n">
         <v>978</v>
@@ -3503,12 +4016,15 @@
         <v>1586</v>
       </c>
       <c r="D82" t="n">
-        <v>0.381435257410296</v>
+        <v>0.38</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B83" t="n">
         <v>31813</v>
@@ -3517,12 +4033,15 @@
         <v>19355</v>
       </c>
       <c r="D83" t="n">
-        <v>0.621736241400876</v>
+        <v>0.62</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B84" t="n">
         <v>599</v>
@@ -3531,12 +4050,15 @@
         <v>923</v>
       </c>
       <c r="D84" t="n">
-        <v>0.393561103810775</v>
+        <v>0.39</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B85" t="n">
         <v>283</v>
@@ -3545,12 +4067,15 @@
         <v>495</v>
       </c>
       <c r="D85" t="n">
-        <v>0.363753213367609</v>
+        <v>0.36</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B86" t="n">
         <v>4128</v>
@@ -3559,12 +4084,15 @@
         <v>3351</v>
       </c>
       <c r="D86" t="n">
-        <v>0.551945447252306</v>
+        <v>0.55</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B87" t="n">
         <v>8513</v>
@@ -3573,12 +4101,15 @@
         <v>13670</v>
       </c>
       <c r="D87" t="n">
-        <v>0.383762340531037</v>
+        <v>0.38</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B88" t="n">
         <v>580</v>
@@ -3587,7 +4118,10 @@
         <v>1104</v>
       </c>
       <c r="D88" t="n">
-        <v>0.344418052256532</v>
+        <v>0.34</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-1.9</v>
       </c>
     </row>
   </sheetData>
@@ -3603,7 +4137,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>25</v>
@@ -3614,10 +4148,13 @@
       <c r="D1" t="s">
         <v>27</v>
       </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B2" t="n">
         <v>57</v>
@@ -3626,12 +4163,15 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.982758620689655</v>
+        <v>0.98</v>
+      </c>
+      <c r="E2" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" t="n">
         <v>1058</v>
@@ -3640,12 +4180,15 @@
         <v>75</v>
       </c>
       <c r="D3" t="n">
-        <v>0.933804060017652</v>
+        <v>0.93</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B4" t="n">
         <v>254</v>
@@ -3654,12 +4197,15 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.903914590747331</v>
+        <v>0.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" t="n">
         <v>288</v>
@@ -3668,12 +4214,15 @@
         <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>0.908517350157729</v>
+        <v>0.91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" t="n">
         <v>259</v>
@@ -3682,12 +4231,15 @@
         <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>0.931654676258993</v>
+        <v>0.93</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="n">
         <v>284</v>
@@ -3696,12 +4248,15 @@
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>0.934210526315789</v>
+        <v>0.93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="n">
         <v>936</v>
@@ -3710,12 +4265,15 @@
         <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>0.930417495029821</v>
+        <v>0.93</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" t="n">
         <v>401</v>
@@ -3724,12 +4282,15 @@
         <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>0.911363636363636</v>
+        <v>0.91</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="n">
         <v>158</v>
@@ -3738,12 +4299,15 @@
         <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>0.814432989690722</v>
+        <v>0.81</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11" t="n">
         <v>1015</v>
@@ -3752,12 +4316,15 @@
         <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>0.919384057971015</v>
+        <v>0.92</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" t="n">
         <v>139</v>
@@ -3766,12 +4333,15 @@
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>0.852760736196319</v>
+        <v>0.85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" t="n">
         <v>169</v>
@@ -3780,12 +4350,15 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>0.820388349514563</v>
+        <v>0.82</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" t="n">
         <v>121</v>
@@ -3794,12 +4367,15 @@
         <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>0.812080536912752</v>
+        <v>0.81</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="n">
         <v>615</v>
@@ -3808,12 +4384,15 @@
         <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>0.922038980509745</v>
+        <v>0.92</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="n">
         <v>540</v>
@@ -3822,12 +4401,15 @@
         <v>115</v>
       </c>
       <c r="D16" t="n">
-        <v>0.824427480916031</v>
+        <v>0.82</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="n">
         <v>295</v>
@@ -3836,12 +4418,15 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>0.919003115264797</v>
+        <v>0.92</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="n">
         <v>604</v>
@@ -3850,12 +4435,15 @@
         <v>88</v>
       </c>
       <c r="D18" t="n">
-        <v>0.872832369942196</v>
+        <v>0.87</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="n">
         <v>1022</v>
@@ -3864,12 +4452,15 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>0.955140186915888</v>
+        <v>0.96</v>
+      </c>
+      <c r="E19" t="n">
+        <v>21.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" t="n">
         <v>891</v>
@@ -3878,12 +4469,15 @@
         <v>82</v>
       </c>
       <c r="D20" t="n">
-        <v>0.915724563206578</v>
+        <v>0.92</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B21" t="n">
         <v>794</v>
@@ -3892,12 +4486,15 @@
         <v>78</v>
       </c>
       <c r="D21" t="n">
-        <v>0.910550458715596</v>
+        <v>0.91</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B22" t="n">
         <v>701</v>
@@ -3906,12 +4503,15 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>0.911573472041612</v>
+        <v>0.91</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B23" t="n">
         <v>521</v>
@@ -3920,12 +4520,15 @@
         <v>67</v>
       </c>
       <c r="D23" t="n">
-        <v>0.886054421768708</v>
+        <v>0.89</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B24" t="n">
         <v>269</v>
@@ -3934,12 +4537,15 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>0.835403726708075</v>
+        <v>0.84</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" t="n">
         <v>717</v>
@@ -3948,12 +4554,15 @@
         <v>86</v>
       </c>
       <c r="D25" t="n">
-        <v>0.892901618929016</v>
+        <v>0.89</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B26" t="n">
         <v>409</v>
@@ -3962,12 +4571,15 @@
         <v>49</v>
       </c>
       <c r="D26" t="n">
-        <v>0.893013100436681</v>
+        <v>0.89</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B27" t="n">
         <v>57</v>
@@ -3976,12 +4588,15 @@
         <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>0.791666666666667</v>
+        <v>0.79</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" t="n">
         <v>1246</v>
@@ -3990,12 +4605,15 @@
         <v>152</v>
       </c>
       <c r="D28" t="n">
-        <v>0.891273247496423</v>
+        <v>0.89</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B29" t="n">
         <v>1440</v>
@@ -4004,12 +4622,15 @@
         <v>148</v>
       </c>
       <c r="D29" t="n">
-        <v>0.906801007556675</v>
+        <v>0.91</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B30" t="n">
         <v>1254</v>
@@ -4018,12 +4639,15 @@
         <v>152</v>
       </c>
       <c r="D30" t="n">
-        <v>0.891891891891892</v>
+        <v>0.89</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B31" t="n">
         <v>1315</v>
@@ -4032,12 +4656,15 @@
         <v>120</v>
       </c>
       <c r="D31" t="n">
-        <v>0.916376306620209</v>
+        <v>0.92</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B32" t="n">
         <v>602</v>
@@ -4046,12 +4673,15 @@
         <v>75</v>
       </c>
       <c r="D32" t="n">
-        <v>0.889217134416544</v>
+        <v>0.89</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B33" t="n">
         <v>858</v>
@@ -4060,12 +4690,15 @@
         <v>122</v>
       </c>
       <c r="D33" t="n">
-        <v>0.875510204081633</v>
+        <v>0.88</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B34" t="n">
         <v>469</v>
@@ -4074,12 +4707,15 @@
         <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>0.967010309278351</v>
+        <v>0.97</v>
+      </c>
+      <c r="E34" t="n">
+        <v>29.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B35" t="n">
         <v>659</v>
@@ -4088,12 +4724,15 @@
         <v>49</v>
       </c>
       <c r="D35" t="n">
-        <v>0.930790960451977</v>
+        <v>0.93</v>
+      </c>
+      <c r="E35" t="n">
+        <v>13.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B36" t="n">
         <v>1213</v>
@@ -4102,12 +4741,15 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.909977494373593</v>
+        <v>0.91</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B37" t="n">
         <v>1159</v>
@@ -4116,12 +4758,15 @@
         <v>179</v>
       </c>
       <c r="D37" t="n">
-        <v>0.866218236173393</v>
+        <v>0.87</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B38" t="n">
         <v>692</v>
@@ -4130,12 +4775,15 @@
         <v>83</v>
       </c>
       <c r="D38" t="n">
-        <v>0.892903225806452</v>
+        <v>0.89</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B39" t="n">
         <v>204</v>
@@ -4144,12 +4792,15 @@
         <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>0.940092165898618</v>
+        <v>0.94</v>
+      </c>
+      <c r="E39" t="n">
+        <v>15.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B40" t="n">
         <v>1057</v>
@@ -4158,12 +4809,15 @@
         <v>91</v>
       </c>
       <c r="D40" t="n">
-        <v>0.920731707317073</v>
+        <v>0.92</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" t="n">
         <v>722</v>
@@ -4172,12 +4826,15 @@
         <v>27</v>
       </c>
       <c r="D41" t="n">
-        <v>0.963951935914553</v>
+        <v>0.96</v>
+      </c>
+      <c r="E41" t="n">
+        <v>26.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" t="n">
         <v>667</v>
@@ -4186,12 +4843,15 @@
         <v>38</v>
       </c>
       <c r="D42" t="n">
-        <v>0.946099290780142</v>
+        <v>0.95</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" t="n">
         <v>810</v>
@@ -4200,12 +4860,15 @@
         <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>0.950704225352113</v>
+        <v>0.95</v>
+      </c>
+      <c r="E43" t="n">
+        <v>19.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" t="n">
         <v>807</v>
@@ -4214,12 +4877,15 @@
         <v>85</v>
       </c>
       <c r="D44" t="n">
-        <v>0.904708520179372</v>
+        <v>0.9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9.49</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" t="n">
         <v>504</v>
@@ -4228,12 +4894,15 @@
         <v>57</v>
       </c>
       <c r="D45" t="n">
-        <v>0.898395721925134</v>
+        <v>0.9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>8.84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" t="n">
         <v>944</v>
@@ -4242,12 +4911,15 @@
         <v>76</v>
       </c>
       <c r="D46" t="n">
-        <v>0.925490196078431</v>
+        <v>0.93</v>
+      </c>
+      <c r="E46" t="n">
+        <v>12.42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" t="n">
         <v>982</v>
@@ -4256,12 +4928,15 @@
         <v>72</v>
       </c>
       <c r="D47" t="n">
-        <v>0.93168880455408</v>
+        <v>0.93</v>
+      </c>
+      <c r="E47" t="n">
+        <v>13.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" t="n">
         <v>827</v>
@@ -4270,12 +4945,15 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>0.907793633369923</v>
+        <v>0.91</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.85</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B49" t="n">
         <v>342</v>
@@ -4284,12 +4962,15 @@
         <v>37</v>
       </c>
       <c r="D49" t="n">
-        <v>0.902374670184697</v>
+        <v>0.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" t="n">
         <v>433</v>
@@ -4298,12 +4979,15 @@
         <v>23</v>
       </c>
       <c r="D50" t="n">
-        <v>0.949561403508772</v>
+        <v>0.95</v>
+      </c>
+      <c r="E50" t="n">
+        <v>18.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B51" t="n">
         <v>450</v>
@@ -4312,12 +4996,15 @@
         <v>65</v>
       </c>
       <c r="D51" t="n">
-        <v>0.87378640776699</v>
+        <v>0.87</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6.92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" t="n">
         <v>926</v>
@@ -4326,12 +5013,15 @@
         <v>107</v>
       </c>
       <c r="D52" t="n">
-        <v>0.896418199419167</v>
+        <v>0.9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>8.65</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B53" t="n">
         <v>921</v>
@@ -4340,12 +5030,15 @@
         <v>138</v>
       </c>
       <c r="D53" t="n">
-        <v>0.869688385269122</v>
+        <v>0.87</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6.67</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B54" t="n">
         <v>976</v>
@@ -4354,12 +5047,15 @@
         <v>171</v>
       </c>
       <c r="D54" t="n">
-        <v>0.850915431560593</v>
+        <v>0.85</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5.71</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B55" t="n">
         <v>507</v>
@@ -4368,12 +5064,15 @@
         <v>56</v>
       </c>
       <c r="D55" t="n">
-        <v>0.900532859680284</v>
+        <v>0.9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B56" t="n">
         <v>846</v>
@@ -4382,12 +5081,15 @@
         <v>103</v>
       </c>
       <c r="D56" t="n">
-        <v>0.891464699683878</v>
+        <v>0.89</v>
+      </c>
+      <c r="E56" t="n">
+        <v>8.21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B57" t="n">
         <v>625</v>
@@ -4396,12 +5098,15 @@
         <v>116</v>
       </c>
       <c r="D57" t="n">
-        <v>0.843454790823212</v>
+        <v>0.84</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B58" t="n">
         <v>118</v>
@@ -4410,12 +5115,15 @@
         <v>34</v>
       </c>
       <c r="D58" t="n">
-        <v>0.776315789473684</v>
+        <v>0.78</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.47</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B59" t="n">
         <v>295</v>
@@ -4424,12 +5132,15 @@
         <v>74</v>
       </c>
       <c r="D59" t="n">
-        <v>0.799457994579946</v>
+        <v>0.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B60" t="n">
         <v>346</v>
@@ -4438,12 +5149,15 @@
         <v>83</v>
       </c>
       <c r="D60" t="n">
-        <v>0.806526806526807</v>
+        <v>0.81</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" t="n">
         <v>293</v>
@@ -4452,12 +5166,15 @@
         <v>55</v>
       </c>
       <c r="D61" t="n">
-        <v>0.841954022988506</v>
+        <v>0.84</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B62" t="n">
         <v>189</v>
@@ -4466,12 +5183,15 @@
         <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>0.79746835443038</v>
+        <v>0.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3.94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B63" t="n">
         <v>182</v>
@@ -4480,12 +5200,15 @@
         <v>13</v>
       </c>
       <c r="D63" t="n">
-        <v>0.933333333333333</v>
+        <v>0.93</v>
+      </c>
+      <c r="E63" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B64" t="n">
         <v>182</v>
@@ -4494,12 +5217,15 @@
         <v>45</v>
       </c>
       <c r="D64" t="n">
-        <v>0.801762114537445</v>
+        <v>0.8</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B65" t="n">
         <v>490</v>
@@ -4508,12 +5234,15 @@
         <v>73</v>
       </c>
       <c r="D65" t="n">
-        <v>0.870337477797513</v>
+        <v>0.87</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6.71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B66" t="n">
         <v>208</v>
@@ -4522,12 +5251,15 @@
         <v>77</v>
       </c>
       <c r="D66" t="n">
-        <v>0.729824561403509</v>
+        <v>0.73</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B67" t="n">
         <v>176</v>
@@ -4536,12 +5268,15 @@
         <v>52</v>
       </c>
       <c r="D67" t="n">
-        <v>0.771929824561403</v>
+        <v>0.77</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3.38</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B68" t="n">
         <v>259</v>
@@ -4550,12 +5285,15 @@
         <v>81</v>
       </c>
       <c r="D68" t="n">
-        <v>0.761764705882353</v>
+        <v>0.76</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B69" t="n">
         <v>175</v>
@@ -4564,12 +5302,15 @@
         <v>36</v>
       </c>
       <c r="D69" t="n">
-        <v>0.829383886255924</v>
+        <v>0.83</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4.86</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B70" t="n">
         <v>124</v>
@@ -4578,12 +5319,15 @@
         <v>41</v>
       </c>
       <c r="D70" t="n">
-        <v>0.751515151515151</v>
+        <v>0.75</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3.02</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B71" t="n">
         <v>186</v>
@@ -4592,12 +5336,15 @@
         <v>44</v>
       </c>
       <c r="D71" t="n">
-        <v>0.808695652173913</v>
+        <v>0.81</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4.23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B72" t="n">
         <v>176</v>
@@ -4606,12 +5353,15 @@
         <v>84</v>
       </c>
       <c r="D72" t="n">
-        <v>0.676923076923077</v>
+        <v>0.68</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B73" t="n">
         <v>267</v>
@@ -4620,12 +5370,15 @@
         <v>106</v>
       </c>
       <c r="D73" t="n">
-        <v>0.715817694369973</v>
+        <v>0.72</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B74" t="n">
         <v>323</v>
@@ -4634,12 +5387,15 @@
         <v>121</v>
       </c>
       <c r="D74" t="n">
-        <v>0.727477477477477</v>
+        <v>0.73</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.67</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B75" t="n">
         <v>247</v>
@@ -4648,12 +5404,15 @@
         <v>43</v>
       </c>
       <c r="D75" t="n">
-        <v>0.851724137931035</v>
+        <v>0.85</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5.74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B76" t="n">
         <v>98</v>
@@ -4662,12 +5421,15 @@
         <v>25</v>
       </c>
       <c r="D76" t="n">
-        <v>0.796747967479675</v>
+        <v>0.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B77" t="n">
         <v>178</v>
@@ -4676,12 +5438,15 @@
         <v>32</v>
       </c>
       <c r="D77" t="n">
-        <v>0.847619047619048</v>
+        <v>0.85</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B78" t="n">
         <v>223</v>
@@ -4690,12 +5455,15 @@
         <v>53</v>
       </c>
       <c r="D78" t="n">
-        <v>0.807971014492754</v>
+        <v>0.81</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4.21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B79" t="n">
         <v>325</v>
@@ -4704,12 +5472,15 @@
         <v>74</v>
       </c>
       <c r="D79" t="n">
-        <v>0.81453634085213</v>
+        <v>0.81</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4.39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B80" t="n">
         <v>198</v>
@@ -4718,12 +5489,15 @@
         <v>67</v>
       </c>
       <c r="D80" t="n">
-        <v>0.747169811320755</v>
+        <v>0.75</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.96</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B81" t="n">
         <v>149</v>
@@ -4732,12 +5506,15 @@
         <v>52</v>
       </c>
       <c r="D81" t="n">
-        <v>0.741293532338308</v>
+        <v>0.74</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B82" t="n">
         <v>334</v>
@@ -4746,12 +5523,15 @@
         <v>90</v>
       </c>
       <c r="D82" t="n">
-        <v>0.787735849056604</v>
+        <v>0.79</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3.71</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B83" t="n">
         <v>218</v>
@@ -4760,12 +5540,15 @@
         <v>100</v>
       </c>
       <c r="D83" t="n">
-        <v>0.685534591194969</v>
+        <v>0.69</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.18</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B84" t="n">
         <v>264</v>
@@ -4774,12 +5557,15 @@
         <v>90</v>
       </c>
       <c r="D84" t="n">
-        <v>0.745762711864407</v>
+        <v>0.75</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" t="n">
         <v>127</v>
@@ -4788,12 +5574,15 @@
         <v>28</v>
       </c>
       <c r="D85" t="n">
-        <v>0.819354838709677</v>
+        <v>0.82</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4.54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B86" t="n">
         <v>406</v>
@@ -4802,12 +5591,15 @@
         <v>78</v>
       </c>
       <c r="D86" t="n">
-        <v>0.838842975206612</v>
+        <v>0.84</v>
+      </c>
+      <c r="E86" t="n">
+        <v>5.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B87" t="n">
         <v>434</v>
@@ -4816,7 +5608,10 @@
         <v>129</v>
       </c>
       <c r="D87" t="n">
-        <v>0.770870337477798</v>
+        <v>0.77</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>
@@ -4835,10 +5630,13 @@
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C1" t="s">
         <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -4849,7 +5647,10 @@
         <v>39507</v>
       </c>
       <c r="C2" t="n">
-        <v>0.939577884835972</v>
+        <v>0.94</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15.55</v>
       </c>
     </row>
   </sheetData>
@@ -4865,21 +5666,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
         <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="n">
         <v>1588</v>
@@ -4888,12 +5692,15 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.984500929944203</v>
+        <v>0.98</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="n">
         <v>31324</v>
@@ -4902,12 +5709,15 @@
         <v>1847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.944318832715324</v>
+        <v>0.94</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="n">
         <v>2290</v>
@@ -4916,12 +5726,15 @@
         <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>0.979050876442924</v>
+        <v>0.98</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="n">
         <v>3659</v>
@@ -4930,12 +5743,15 @@
         <v>146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.961629434954008</v>
+        <v>0.96</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="n">
         <v>1904</v>
@@ -4944,12 +5760,15 @@
         <v>124</v>
       </c>
       <c r="D6" t="n">
-        <v>0.938856015779093</v>
+        <v>0.94</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="n">
         <v>392</v>
@@ -4958,12 +5777,15 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.98989898989899</v>
+        <v>0.99</v>
+      </c>
+      <c r="E7" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="n">
         <v>5508</v>
@@ -4972,12 +5794,15 @@
         <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>0.936416184971098</v>
+        <v>0.94</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="n">
         <v>1606</v>
@@ -4986,12 +5811,15 @@
         <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>0.976885644768856</v>
+        <v>0.98</v>
+      </c>
+      <c r="E9" t="n">
+        <v>42.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="n">
         <v>3892</v>
@@ -5000,12 +5828,15 @@
         <v>114</v>
       </c>
       <c r="D10" t="n">
-        <v>0.971542685971043</v>
+        <v>0.97</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="n">
         <v>10215</v>
@@ -5014,12 +5845,15 @@
         <v>348</v>
       </c>
       <c r="D11" t="n">
-        <v>0.967054813973303</v>
+        <v>0.97</v>
+      </c>
+      <c r="E11" t="n">
+        <v>29.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="n">
         <v>2327</v>
@@ -5028,12 +5862,15 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>0.979377104377104</v>
+        <v>0.98</v>
+      </c>
+      <c r="E12" t="n">
+        <v>47.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>724</v>
@@ -5042,12 +5879,15 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>0.965333333333333</v>
+        <v>0.97</v>
+      </c>
+      <c r="E13" t="n">
+        <v>27.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="n">
         <v>3944</v>
@@ -5056,12 +5896,15 @@
         <v>149</v>
       </c>
       <c r="D14" t="n">
-        <v>0.963596384070364</v>
+        <v>0.96</v>
+      </c>
+      <c r="E14" t="n">
+        <v>26.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="n">
         <v>5106</v>
@@ -5070,12 +5913,15 @@
         <v>349</v>
       </c>
       <c r="D15" t="n">
-        <v>0.936021998166819</v>
+        <v>0.94</v>
+      </c>
+      <c r="E15" t="n">
+        <v>14.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
         <v>496</v>
@@ -5084,12 +5930,15 @@
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>0.953846153846154</v>
+        <v>0.95</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
         <v>1403</v>
@@ -5098,12 +5947,15 @@
         <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>0.970262793914246</v>
+        <v>0.97</v>
+      </c>
+      <c r="E17" t="n">
+        <v>32.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="n">
         <v>423</v>
@@ -5112,12 +5964,15 @@
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>0.963553530751708</v>
+        <v>0.96</v>
+      </c>
+      <c r="E18" t="n">
+        <v>26.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="n">
         <v>4884</v>
@@ -5126,12 +5981,15 @@
         <v>127</v>
       </c>
       <c r="D19" t="n">
-        <v>0.974655757333865</v>
+        <v>0.97</v>
+      </c>
+      <c r="E19" t="n">
+        <v>38.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="n">
         <v>55404</v>
@@ -5140,12 +5998,15 @@
         <v>2813</v>
       </c>
       <c r="D20" t="n">
-        <v>0.951680780528024</v>
+        <v>0.95</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" t="n">
         <v>1043</v>
@@ -5154,12 +6015,15 @@
         <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>0.956003666361137</v>
+        <v>0.96</v>
+      </c>
+      <c r="E21" t="n">
+        <v>21.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" t="n">
         <v>2895</v>
@@ -5168,12 +6032,15 @@
         <v>76</v>
       </c>
       <c r="D22" t="n">
-        <v>0.974419387411646</v>
+        <v>0.97</v>
+      </c>
+      <c r="E22" t="n">
+        <v>38.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="n">
         <v>1118</v>
@@ -5182,12 +6049,15 @@
         <v>37</v>
       </c>
       <c r="D23" t="n">
-        <v>0.967965367965368</v>
+        <v>0.97</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" t="n">
         <v>1537</v>
@@ -5196,12 +6066,15 @@
         <v>42</v>
       </c>
       <c r="D24" t="n">
-        <v>0.973400886637112</v>
+        <v>0.97</v>
+      </c>
+      <c r="E24" t="n">
+        <v>36.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="n">
         <v>1973</v>
@@ -5210,12 +6083,15 @@
         <v>52</v>
       </c>
       <c r="D25" t="n">
-        <v>0.974320987654321</v>
+        <v>0.97</v>
+      </c>
+      <c r="E25" t="n">
+        <v>37.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" t="n">
         <v>4306</v>
@@ -5224,12 +6100,15 @@
         <v>145</v>
       </c>
       <c r="D26" t="n">
-        <v>0.967423050999775</v>
+        <v>0.97</v>
+      </c>
+      <c r="E26" t="n">
+        <v>29.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" t="n">
         <v>540</v>
@@ -5238,12 +6117,15 @@
         <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>0.974729241877256</v>
+        <v>0.97</v>
+      </c>
+      <c r="E27" t="n">
+        <v>38.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" t="n">
         <v>204781</v>
@@ -5252,12 +6134,15 @@
         <v>18093</v>
       </c>
       <c r="D28" t="n">
-        <v>0.91881960210702</v>
+        <v>0.92</v>
+      </c>
+      <c r="E28" t="n">
+        <v>11.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" t="n">
         <v>1351</v>
@@ -5266,12 +6151,15 @@
         <v>40</v>
       </c>
       <c r="D29" t="n">
-        <v>0.971243709561467</v>
+        <v>0.97</v>
+      </c>
+      <c r="E29" t="n">
+        <v>33.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" t="n">
         <v>1749</v>
@@ -5280,12 +6168,15 @@
         <v>43</v>
       </c>
       <c r="D30" t="n">
-        <v>0.976004464285714</v>
+        <v>0.98</v>
+      </c>
+      <c r="E30" t="n">
+        <v>40.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B31" t="n">
         <v>2492</v>
@@ -5294,12 +6185,15 @@
         <v>91</v>
       </c>
       <c r="D31" t="n">
-        <v>0.964769647696477</v>
+        <v>0.96</v>
+      </c>
+      <c r="E31" t="n">
+        <v>27.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" t="n">
         <v>4298</v>
@@ -5308,12 +6202,15 @@
         <v>77</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9824</v>
+        <v>0.98</v>
+      </c>
+      <c r="E32" t="n">
+        <v>55.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" t="n">
         <v>498</v>
@@ -5322,12 +6219,15 @@
         <v>21</v>
       </c>
       <c r="D33" t="n">
-        <v>0.959537572254335</v>
+        <v>0.96</v>
+      </c>
+      <c r="E33" t="n">
+        <v>23.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B34" t="n">
         <v>914</v>
@@ -5336,12 +6236,15 @@
         <v>27</v>
       </c>
       <c r="D34" t="n">
-        <v>0.971307120085016</v>
+        <v>0.97</v>
+      </c>
+      <c r="E34" t="n">
+        <v>33.85</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" t="n">
         <v>2807</v>
@@ -5350,12 +6253,15 @@
         <v>78</v>
       </c>
       <c r="D35" t="n">
-        <v>0.972963604852686</v>
+        <v>0.97</v>
+      </c>
+      <c r="E35" t="n">
+        <v>35.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36" t="n">
         <v>457</v>
@@ -5364,12 +6270,15 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.989177489177489</v>
+        <v>0.99</v>
+      </c>
+      <c r="E36" t="n">
+        <v>91.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B37" t="n">
         <v>1023</v>
@@ -5378,12 +6287,15 @@
         <v>21</v>
       </c>
       <c r="D37" t="n">
-        <v>0.979885057471264</v>
+        <v>0.98</v>
+      </c>
+      <c r="E37" t="n">
+        <v>48.71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B38" t="n">
         <v>505</v>
@@ -5392,12 +6304,15 @@
         <v>20</v>
       </c>
       <c r="D38" t="n">
-        <v>0.961904761904762</v>
+        <v>0.96</v>
+      </c>
+      <c r="E38" t="n">
+        <v>25.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B39" t="n">
         <v>1602</v>
@@ -5406,12 +6321,15 @@
         <v>47</v>
       </c>
       <c r="D39" t="n">
-        <v>0.971497877501516</v>
+        <v>0.97</v>
+      </c>
+      <c r="E39" t="n">
+        <v>34.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B40" t="n">
         <v>250</v>
@@ -5420,12 +6338,15 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>0.984251968503937</v>
+        <v>0.98</v>
+      </c>
+      <c r="E40" t="n">
+        <v>62.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B41" t="n">
         <v>2020</v>
@@ -5434,12 +6355,15 @@
         <v>57</v>
       </c>
       <c r="D41" t="n">
-        <v>0.972556571978816</v>
+        <v>0.97</v>
+      </c>
+      <c r="E41" t="n">
+        <v>35.44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B42" t="n">
         <v>276</v>
@@ -5448,12 +6372,15 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.98220640569395</v>
+        <v>0.98</v>
+      </c>
+      <c r="E42" t="n">
+        <v>55.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B43" t="n">
         <v>1301</v>
@@ -5462,12 +6389,15 @@
         <v>37</v>
       </c>
       <c r="D43" t="n">
-        <v>0.972346786248132</v>
+        <v>0.97</v>
+      </c>
+      <c r="E43" t="n">
+        <v>35.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B44" t="n">
         <v>378</v>
@@ -5476,12 +6406,15 @@
         <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>0.974226804123711</v>
+        <v>0.97</v>
+      </c>
+      <c r="E44" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B45" t="n">
         <v>451</v>
@@ -5490,12 +6423,15 @@
         <v>16</v>
       </c>
       <c r="D45" t="n">
-        <v>0.965738758029979</v>
+        <v>0.97</v>
+      </c>
+      <c r="E45" t="n">
+        <v>28.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B46" t="n">
         <v>883</v>
@@ -5504,12 +6440,15 @@
         <v>16</v>
       </c>
       <c r="D46" t="n">
-        <v>0.982202447163515</v>
+        <v>0.98</v>
+      </c>
+      <c r="E46" t="n">
+        <v>55.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B47" t="n">
         <v>1698</v>
@@ -5518,12 +6457,15 @@
         <v>93</v>
       </c>
       <c r="D47" t="n">
-        <v>0.948073701842546</v>
+        <v>0.95</v>
+      </c>
+      <c r="E47" t="n">
+        <v>18.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B48" t="n">
         <v>1204</v>
@@ -5532,12 +6474,15 @@
         <v>23</v>
       </c>
       <c r="D48" t="n">
-        <v>0.981255093724531</v>
+        <v>0.98</v>
+      </c>
+      <c r="E48" t="n">
+        <v>52.35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B49" t="n">
         <v>1281</v>
@@ -5546,12 +6491,15 @@
         <v>60</v>
       </c>
       <c r="D49" t="n">
-        <v>0.955257270693512</v>
+        <v>0.96</v>
+      </c>
+      <c r="E49" t="n">
+        <v>21.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B50" t="n">
         <v>1375</v>
@@ -5560,12 +6508,15 @@
         <v>44</v>
       </c>
       <c r="D50" t="n">
-        <v>0.968992248062015</v>
+        <v>0.97</v>
+      </c>
+      <c r="E50" t="n">
+        <v>31.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B51" t="n">
         <v>2268</v>
@@ -5574,12 +6525,15 @@
         <v>85</v>
       </c>
       <c r="D51" t="n">
-        <v>0.963875903102422</v>
+        <v>0.96</v>
+      </c>
+      <c r="E51" t="n">
+        <v>26.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B52" t="n">
         <v>452</v>
@@ -5588,12 +6542,15 @@
         <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>0.978354978354978</v>
+        <v>0.98</v>
+      </c>
+      <c r="E52" t="n">
+        <v>45.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B53" t="n">
         <v>3070</v>
@@ -5602,12 +6559,15 @@
         <v>164</v>
       </c>
       <c r="D53" t="n">
-        <v>0.949288806431664</v>
+        <v>0.95</v>
+      </c>
+      <c r="E53" t="n">
+        <v>18.72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B54" t="n">
         <v>645</v>
@@ -5616,12 +6576,15 @@
         <v>34</v>
       </c>
       <c r="D54" t="n">
-        <v>0.949926362297496</v>
+        <v>0.95</v>
+      </c>
+      <c r="E54" t="n">
+        <v>18.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B55" t="n">
         <v>570</v>
@@ -5630,12 +6593,15 @@
         <v>15</v>
       </c>
       <c r="D55" t="n">
-        <v>0.974358974358974</v>
+        <v>0.97</v>
+      </c>
+      <c r="E55" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B56" t="n">
         <v>17444</v>
@@ -5644,12 +6610,15 @@
         <v>862</v>
       </c>
       <c r="D56" t="n">
-        <v>0.952911613678575</v>
+        <v>0.95</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20.24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B57" t="n">
         <v>3825</v>
@@ -5658,12 +6627,15 @@
         <v>71</v>
       </c>
       <c r="D57" t="n">
-        <v>0.981776180698152</v>
+        <v>0.98</v>
+      </c>
+      <c r="E57" t="n">
+        <v>53.87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B58" t="n">
         <v>516</v>
@@ -5672,12 +6644,15 @@
         <v>23</v>
       </c>
       <c r="D58" t="n">
-        <v>0.957328385899815</v>
+        <v>0.96</v>
+      </c>
+      <c r="E58" t="n">
+        <v>22.43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B59" t="n">
         <v>1933</v>
@@ -5686,12 +6661,15 @@
         <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>0.974785678265255</v>
+        <v>0.97</v>
+      </c>
+      <c r="E59" t="n">
+        <v>38.66</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B60" t="n">
         <v>478</v>
@@ -5700,12 +6678,15 @@
         <v>17</v>
       </c>
       <c r="D60" t="n">
-        <v>0.965656565656566</v>
+        <v>0.97</v>
+      </c>
+      <c r="E60" t="n">
+        <v>28.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B61" t="n">
         <v>1482</v>
@@ -5714,12 +6695,15 @@
         <v>63</v>
       </c>
       <c r="D61" t="n">
-        <v>0.959223300970874</v>
+        <v>0.96</v>
+      </c>
+      <c r="E61" t="n">
+        <v>23.52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B62" t="n">
         <v>864</v>
@@ -5728,12 +6712,15 @@
         <v>16</v>
       </c>
       <c r="D62" t="n">
-        <v>0.981818181818182</v>
+        <v>0.98</v>
+      </c>
+      <c r="E62" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B63" t="n">
         <v>78614</v>
@@ -5742,12 +6729,15 @@
         <v>6997</v>
       </c>
       <c r="D63" t="n">
-        <v>0.918269848500777</v>
+        <v>0.92</v>
+      </c>
+      <c r="E63" t="n">
+        <v>11.24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B64" t="n">
         <v>257</v>
@@ -5756,12 +6746,15 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.992277992277992</v>
+        <v>0.99</v>
+      </c>
+      <c r="E64" t="n">
+        <v>128.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B65" t="n">
         <v>734</v>
@@ -5770,12 +6763,15 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>0.955729166666667</v>
+        <v>0.96</v>
+      </c>
+      <c r="E65" t="n">
+        <v>21.59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B66" t="n">
         <v>611</v>
@@ -5784,12 +6780,15 @@
         <v>17</v>
       </c>
       <c r="D66" t="n">
-        <v>0.972929936305732</v>
+        <v>0.97</v>
+      </c>
+      <c r="E66" t="n">
+        <v>35.94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B67" t="n">
         <v>6436</v>
@@ -5798,12 +6797,15 @@
         <v>280</v>
       </c>
       <c r="D67" t="n">
-        <v>0.95830851697439</v>
+        <v>0.96</v>
+      </c>
+      <c r="E67" t="n">
+        <v>22.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B68" t="n">
         <v>561</v>
@@ -5812,12 +6814,15 @@
         <v>37</v>
       </c>
       <c r="D68" t="n">
-        <v>0.938127090301003</v>
+        <v>0.94</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15.16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B69" t="n">
         <v>574</v>
@@ -5826,12 +6831,15 @@
         <v>26</v>
       </c>
       <c r="D69" t="n">
-        <v>0.956666666666667</v>
+        <v>0.96</v>
+      </c>
+      <c r="E69" t="n">
+        <v>22.08</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B70" t="n">
         <v>12895</v>
@@ -5840,12 +6848,15 @@
         <v>629</v>
       </c>
       <c r="D70" t="n">
-        <v>0.953490091688849</v>
+        <v>0.95</v>
+      </c>
+      <c r="E70" t="n">
+        <v>20.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B71" t="n">
         <v>4867</v>
@@ -5854,12 +6865,15 @@
         <v>284</v>
       </c>
       <c r="D71" t="n">
-        <v>0.944865074742768</v>
+        <v>0.94</v>
+      </c>
+      <c r="E71" t="n">
+        <v>17.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B72" t="n">
         <v>1013</v>
@@ -5868,12 +6882,15 @@
         <v>36</v>
       </c>
       <c r="D72" t="n">
-        <v>0.965681601525262</v>
+        <v>0.97</v>
+      </c>
+      <c r="E72" t="n">
+        <v>28.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B73" t="n">
         <v>26010</v>
@@ -5882,12 +6899,15 @@
         <v>1035</v>
       </c>
       <c r="D73" t="n">
-        <v>0.961730449251248</v>
+        <v>0.96</v>
+      </c>
+      <c r="E73" t="n">
+        <v>25.13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B74" t="n">
         <v>10054</v>
@@ -5896,12 +6916,15 @@
         <v>482</v>
       </c>
       <c r="D74" t="n">
-        <v>0.954252088078967</v>
+        <v>0.95</v>
+      </c>
+      <c r="E74" t="n">
+        <v>20.86</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B75" t="n">
         <v>2231</v>
@@ -5910,12 +6933,15 @@
         <v>75</v>
       </c>
       <c r="D75" t="n">
-        <v>0.967476149176062</v>
+        <v>0.97</v>
+      </c>
+      <c r="E75" t="n">
+        <v>29.75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B76" t="n">
         <v>640</v>
@@ -5924,12 +6950,15 @@
         <v>33</v>
       </c>
       <c r="D76" t="n">
-        <v>0.950965824665676</v>
+        <v>0.95</v>
+      </c>
+      <c r="E76" t="n">
+        <v>19.39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B77" t="n">
         <v>659</v>
@@ -5938,12 +6967,15 @@
         <v>14</v>
       </c>
       <c r="D77" t="n">
-        <v>0.979197622585438</v>
+        <v>0.98</v>
+      </c>
+      <c r="E77" t="n">
+        <v>47.07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B78" t="n">
         <v>1053</v>
@@ -5952,12 +6984,15 @@
         <v>34</v>
       </c>
       <c r="D78" t="n">
-        <v>0.968721251149954</v>
+        <v>0.97</v>
+      </c>
+      <c r="E78" t="n">
+        <v>30.97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B79" t="n">
         <v>192</v>
@@ -5966,12 +7001,15 @@
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>0.989690721649485</v>
+        <v>0.99</v>
+      </c>
+      <c r="E79" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B80" t="n">
         <v>1671</v>
@@ -5980,12 +7018,15 @@
         <v>44</v>
       </c>
       <c r="D80" t="n">
-        <v>0.974344023323615</v>
+        <v>0.97</v>
+      </c>
+      <c r="E80" t="n">
+        <v>37.98</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B81" t="n">
         <v>735</v>
@@ -5994,12 +7035,15 @@
         <v>19</v>
       </c>
       <c r="D81" t="n">
-        <v>0.974801061007958</v>
+        <v>0.97</v>
+      </c>
+      <c r="E81" t="n">
+        <v>38.68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B82" t="n">
         <v>978</v>
@@ -6008,12 +7052,15 @@
         <v>43</v>
       </c>
       <c r="D82" t="n">
-        <v>0.957884427032321</v>
+        <v>0.96</v>
+      </c>
+      <c r="E82" t="n">
+        <v>22.74</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B83" t="n">
         <v>31813</v>
@@ -6022,12 +7069,15 @@
         <v>1349</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9593209094747</v>
+        <v>0.96</v>
+      </c>
+      <c r="E83" t="n">
+        <v>23.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B84" t="n">
         <v>599</v>
@@ -6036,12 +7086,15 @@
         <v>13</v>
       </c>
       <c r="D84" t="n">
-        <v>0.97875816993464</v>
+        <v>0.98</v>
+      </c>
+      <c r="E84" t="n">
+        <v>46.08</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B85" t="n">
         <v>283</v>
@@ -6050,12 +7103,15 @@
         <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>0.975862068965517</v>
+        <v>0.98</v>
+      </c>
+      <c r="E85" t="n">
+        <v>40.43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B86" t="n">
         <v>4128</v>
@@ -6064,12 +7120,15 @@
         <v>213</v>
       </c>
       <c r="D86" t="n">
-        <v>0.950932964754665</v>
+        <v>0.95</v>
+      </c>
+      <c r="E86" t="n">
+        <v>19.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B87" t="n">
         <v>8513</v>
@@ -6078,12 +7137,15 @@
         <v>365</v>
       </c>
       <c r="D87" t="n">
-        <v>0.95888713674251</v>
+        <v>0.96</v>
+      </c>
+      <c r="E87" t="n">
+        <v>23.32</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B88" t="n">
         <v>580</v>
@@ -6092,7 +7154,10 @@
         <v>20</v>
       </c>
       <c r="D88" t="n">
-        <v>0.966666666666667</v>
+        <v>0.97</v>
+      </c>
+      <c r="E88" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -6108,21 +7173,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B2" t="n">
         <v>57</v>
@@ -6131,12 +7199,15 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0.890625</v>
+        <v>0.89</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" t="n">
         <v>1058</v>
@@ -6145,12 +7216,15 @@
         <v>110</v>
       </c>
       <c r="D3" t="n">
-        <v>0.905821917808219</v>
+        <v>0.91</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B4" t="n">
         <v>254</v>
@@ -6159,12 +7233,15 @@
         <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>0.822006472491909</v>
+        <v>0.82</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" t="n">
         <v>288</v>
@@ -6173,12 +7250,15 @@
         <v>79</v>
       </c>
       <c r="D5" t="n">
-        <v>0.784741144414169</v>
+        <v>0.78</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" t="n">
         <v>259</v>
@@ -6187,12 +7267,15 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>0.883959044368601</v>
+        <v>0.88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="n">
         <v>284</v>
@@ -6201,12 +7284,15 @@
         <v>52</v>
       </c>
       <c r="D7" t="n">
-        <v>0.845238095238095</v>
+        <v>0.85</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="n">
         <v>936</v>
@@ -6215,12 +7301,15 @@
         <v>110</v>
       </c>
       <c r="D8" t="n">
-        <v>0.894837476099426</v>
+        <v>0.89</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" t="n">
         <v>401</v>
@@ -6229,12 +7318,15 @@
         <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>0.88716814159292</v>
+        <v>0.89</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="n">
         <v>158</v>
@@ -6243,12 +7335,15 @@
         <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>0.763285024154589</v>
+        <v>0.76</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11" t="n">
         <v>1015</v>
@@ -6257,12 +7352,15 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>0.889570552147239</v>
+        <v>0.89</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" t="n">
         <v>139</v>
@@ -6271,12 +7369,15 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>0.926666666666667</v>
+        <v>0.93</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" t="n">
         <v>169</v>
@@ -6285,12 +7386,15 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>0.793427230046948</v>
+        <v>0.79</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" t="n">
         <v>121</v>
@@ -6299,12 +7403,15 @@
         <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>0.817567567567568</v>
+        <v>0.82</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="n">
         <v>615</v>
@@ -6313,12 +7420,15 @@
         <v>83</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8810888252149</v>
+        <v>0.88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="n">
         <v>540</v>
@@ -6327,12 +7437,15 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>0.909090909090909</v>
+        <v>0.91</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="n">
         <v>295</v>
@@ -6341,12 +7454,15 @@
         <v>46</v>
       </c>
       <c r="D17" t="n">
-        <v>0.865102639296188</v>
+        <v>0.87</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="n">
         <v>604</v>
@@ -6355,12 +7471,15 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>0.902840059790732</v>
+        <v>0.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="n">
         <v>1022</v>
@@ -6369,12 +7488,15 @@
         <v>92</v>
       </c>
       <c r="D19" t="n">
-        <v>0.917414721723519</v>
+        <v>0.92</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" t="n">
         <v>891</v>
@@ -6383,12 +7505,15 @@
         <v>83</v>
       </c>
       <c r="D20" t="n">
-        <v>0.914784394250513</v>
+        <v>0.91</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B21" t="n">
         <v>794</v>
@@ -6397,12 +7522,15 @@
         <v>130</v>
       </c>
       <c r="D21" t="n">
-        <v>0.859307359307359</v>
+        <v>0.86</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B22" t="n">
         <v>701</v>
@@ -6411,12 +7539,15 @@
         <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>0.916339869281046</v>
+        <v>0.92</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B23" t="n">
         <v>521</v>
@@ -6425,12 +7556,15 @@
         <v>79</v>
       </c>
       <c r="D23" t="n">
-        <v>0.868333333333333</v>
+        <v>0.87</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B24" t="n">
         <v>269</v>
@@ -6439,12 +7573,15 @@
         <v>42</v>
       </c>
       <c r="D24" t="n">
-        <v>0.864951768488746</v>
+        <v>0.86</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" t="n">
         <v>717</v>
@@ -6453,12 +7590,15 @@
         <v>101</v>
       </c>
       <c r="D25" t="n">
-        <v>0.876528117359413</v>
+        <v>0.88</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B26" t="n">
         <v>409</v>
@@ -6467,12 +7607,15 @@
         <v>53</v>
       </c>
       <c r="D26" t="n">
-        <v>0.885281385281385</v>
+        <v>0.89</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B27" t="n">
         <v>57</v>
@@ -6481,12 +7624,15 @@
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>0.77027027027027</v>
+        <v>0.77</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" t="n">
         <v>1246</v>
@@ -6495,12 +7641,15 @@
         <v>74</v>
       </c>
       <c r="D28" t="n">
-        <v>0.943939393939394</v>
+        <v>0.94</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B29" t="n">
         <v>1440</v>
@@ -6509,12 +7658,15 @@
         <v>97</v>
       </c>
       <c r="D29" t="n">
-        <v>0.936890045543266</v>
+        <v>0.94</v>
+      </c>
+      <c r="E29" t="n">
+        <v>14.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B30" t="n">
         <v>1254</v>
@@ -6523,12 +7675,15 @@
         <v>69</v>
       </c>
       <c r="D30" t="n">
-        <v>0.947845804988662</v>
+        <v>0.95</v>
+      </c>
+      <c r="E30" t="n">
+        <v>18.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B31" t="n">
         <v>1315</v>
@@ -6537,12 +7692,15 @@
         <v>50</v>
       </c>
       <c r="D31" t="n">
-        <v>0.963369963369963</v>
+        <v>0.96</v>
+      </c>
+      <c r="E31" t="n">
+        <v>26.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B32" t="n">
         <v>602</v>
@@ -6551,12 +7709,15 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>0.917682926829268</v>
+        <v>0.92</v>
+      </c>
+      <c r="E32" t="n">
+        <v>11.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B33" t="n">
         <v>858</v>
@@ -6565,12 +7726,15 @@
         <v>47</v>
       </c>
       <c r="D33" t="n">
-        <v>0.948066298342541</v>
+        <v>0.95</v>
+      </c>
+      <c r="E33" t="n">
+        <v>18.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B34" t="n">
         <v>469</v>
@@ -6579,12 +7743,15 @@
         <v>62</v>
       </c>
       <c r="D34" t="n">
-        <v>0.883239171374765</v>
+        <v>0.88</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B35" t="n">
         <v>659</v>
@@ -6593,12 +7760,15 @@
         <v>37</v>
       </c>
       <c r="D35" t="n">
-        <v>0.94683908045977</v>
+        <v>0.95</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B36" t="n">
         <v>1213</v>
@@ -6607,12 +7777,15 @@
         <v>103</v>
       </c>
       <c r="D36" t="n">
-        <v>0.921732522796353</v>
+        <v>0.92</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B37" t="n">
         <v>1159</v>
@@ -6621,12 +7794,15 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>0.940746753246753</v>
+        <v>0.94</v>
+      </c>
+      <c r="E37" t="n">
+        <v>15.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B38" t="n">
         <v>692</v>
@@ -6635,12 +7811,15 @@
         <v>47</v>
       </c>
       <c r="D38" t="n">
-        <v>0.936400541271989</v>
+        <v>0.94</v>
+      </c>
+      <c r="E38" t="n">
+        <v>14.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B39" t="n">
         <v>204</v>
@@ -6649,12 +7828,15 @@
         <v>23</v>
       </c>
       <c r="D39" t="n">
-        <v>0.898678414096916</v>
+        <v>0.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B40" t="n">
         <v>1057</v>
@@ -6663,12 +7845,15 @@
         <v>87</v>
       </c>
       <c r="D40" t="n">
-        <v>0.923951048951049</v>
+        <v>0.92</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" t="n">
         <v>722</v>
@@ -6677,12 +7862,15 @@
         <v>46</v>
       </c>
       <c r="D41" t="n">
-        <v>0.940104166666667</v>
+        <v>0.94</v>
+      </c>
+      <c r="E41" t="n">
+        <v>15.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" t="n">
         <v>667</v>
@@ -6691,12 +7879,15 @@
         <v>79</v>
       </c>
       <c r="D42" t="n">
-        <v>0.894101876675603</v>
+        <v>0.89</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8.44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" t="n">
         <v>810</v>
@@ -6705,12 +7896,15 @@
         <v>138</v>
       </c>
       <c r="D43" t="n">
-        <v>0.854430379746835</v>
+        <v>0.85</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" t="n">
         <v>807</v>
@@ -6719,12 +7913,15 @@
         <v>103</v>
       </c>
       <c r="D44" t="n">
-        <v>0.886813186813187</v>
+        <v>0.89</v>
+      </c>
+      <c r="E44" t="n">
+        <v>7.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" t="n">
         <v>504</v>
@@ -6733,12 +7930,15 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>0.903225806451613</v>
+        <v>0.9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>9.33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" t="n">
         <v>944</v>
@@ -6747,12 +7947,15 @@
         <v>126</v>
       </c>
       <c r="D46" t="n">
-        <v>0.882242990654206</v>
+        <v>0.88</v>
+      </c>
+      <c r="E46" t="n">
+        <v>7.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" t="n">
         <v>982</v>
@@ -6761,12 +7964,15 @@
         <v>195</v>
       </c>
       <c r="D47" t="n">
-        <v>0.834324553950722</v>
+        <v>0.83</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" t="n">
         <v>827</v>
@@ -6775,12 +7981,15 @@
         <v>186</v>
       </c>
       <c r="D48" t="n">
-        <v>0.816386969397828</v>
+        <v>0.82</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B49" t="n">
         <v>342</v>
@@ -6789,12 +7998,15 @@
         <v>51</v>
       </c>
       <c r="D49" t="n">
-        <v>0.870229007633588</v>
+        <v>0.87</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6.71</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" t="n">
         <v>433</v>
@@ -6803,12 +8015,15 @@
         <v>87</v>
       </c>
       <c r="D50" t="n">
-        <v>0.832692307692308</v>
+        <v>0.83</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4.98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B51" t="n">
         <v>450</v>
@@ -6817,12 +8032,15 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>0.875486381322957</v>
+        <v>0.88</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" t="n">
         <v>926</v>
@@ -6831,12 +8049,15 @@
         <v>59</v>
       </c>
       <c r="D52" t="n">
-        <v>0.94010152284264</v>
+        <v>0.94</v>
+      </c>
+      <c r="E52" t="n">
+        <v>15.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B53" t="n">
         <v>921</v>
@@ -6845,12 +8066,15 @@
         <v>64</v>
       </c>
       <c r="D53" t="n">
-        <v>0.93502538071066</v>
+        <v>0.94</v>
+      </c>
+      <c r="E53" t="n">
+        <v>14.39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B54" t="n">
         <v>976</v>
@@ -6859,12 +8083,15 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>0.916431924882629</v>
+        <v>0.92</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B55" t="n">
         <v>507</v>
@@ -6873,12 +8100,15 @@
         <v>41</v>
       </c>
       <c r="D55" t="n">
-        <v>0.925182481751825</v>
+        <v>0.93</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B56" t="n">
         <v>846</v>
@@ -6887,12 +8117,15 @@
         <v>126</v>
       </c>
       <c r="D56" t="n">
-        <v>0.87037037037037</v>
+        <v>0.87</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B57" t="n">
         <v>625</v>
@@ -6901,12 +8134,15 @@
         <v>80</v>
       </c>
       <c r="D57" t="n">
-        <v>0.886524822695035</v>
+        <v>0.89</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B58" t="n">
         <v>118</v>
@@ -6915,12 +8151,15 @@
         <v>25</v>
       </c>
       <c r="D58" t="n">
-        <v>0.825174825174825</v>
+        <v>0.83</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B59" t="n">
         <v>295</v>
@@ -6929,12 +8168,15 @@
         <v>60</v>
       </c>
       <c r="D59" t="n">
-        <v>0.830985915492958</v>
+        <v>0.83</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4.92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B60" t="n">
         <v>346</v>
@@ -6943,12 +8185,15 @@
         <v>44</v>
       </c>
       <c r="D60" t="n">
-        <v>0.887179487179487</v>
+        <v>0.89</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7.86</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" t="n">
         <v>293</v>
@@ -6957,12 +8202,15 @@
         <v>36</v>
       </c>
       <c r="D61" t="n">
-        <v>0.890577507598784</v>
+        <v>0.89</v>
+      </c>
+      <c r="E61" t="n">
+        <v>8.14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B62" t="n">
         <v>189</v>
@@ -6971,12 +8219,15 @@
         <v>54</v>
       </c>
       <c r="D62" t="n">
-        <v>0.777777777777778</v>
+        <v>0.78</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B63" t="n">
         <v>182</v>
@@ -6985,12 +8236,15 @@
         <v>22</v>
       </c>
       <c r="D63" t="n">
-        <v>0.892156862745098</v>
+        <v>0.89</v>
+      </c>
+      <c r="E63" t="n">
+        <v>8.27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B64" t="n">
         <v>182</v>
@@ -6999,12 +8253,15 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>0.834862385321101</v>
+        <v>0.83</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B65" t="n">
         <v>490</v>
@@ -7013,12 +8270,15 @@
         <v>60</v>
       </c>
       <c r="D65" t="n">
-        <v>0.890909090909091</v>
+        <v>0.89</v>
+      </c>
+      <c r="E65" t="n">
+        <v>8.17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B66" t="n">
         <v>208</v>
@@ -7027,12 +8287,15 @@
         <v>28</v>
       </c>
       <c r="D66" t="n">
-        <v>0.88135593220339</v>
+        <v>0.88</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7.43</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B67" t="n">
         <v>176</v>
@@ -7041,12 +8304,15 @@
         <v>26</v>
       </c>
       <c r="D67" t="n">
-        <v>0.871287128712871</v>
+        <v>0.87</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B68" t="n">
         <v>259</v>
@@ -7055,12 +8321,15 @@
         <v>39</v>
       </c>
       <c r="D68" t="n">
-        <v>0.869127516778524</v>
+        <v>0.87</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B69" t="n">
         <v>175</v>
@@ -7069,12 +8338,15 @@
         <v>42</v>
       </c>
       <c r="D69" t="n">
-        <v>0.806451612903226</v>
+        <v>0.81</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4.17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B70" t="n">
         <v>124</v>
@@ -7083,12 +8355,15 @@
         <v>27</v>
       </c>
       <c r="D70" t="n">
-        <v>0.821192052980132</v>
+        <v>0.82</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4.59</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B71" t="n">
         <v>186</v>
@@ -7097,12 +8372,15 @@
         <v>24</v>
       </c>
       <c r="D71" t="n">
-        <v>0.885714285714286</v>
+        <v>0.89</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B72" t="n">
         <v>176</v>
@@ -7111,12 +8389,15 @@
         <v>17</v>
       </c>
       <c r="D72" t="n">
-        <v>0.911917098445596</v>
+        <v>0.91</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B73" t="n">
         <v>267</v>
@@ -7125,12 +8406,15 @@
         <v>21</v>
       </c>
       <c r="D73" t="n">
-        <v>0.927083333333333</v>
+        <v>0.93</v>
+      </c>
+      <c r="E73" t="n">
+        <v>12.71</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B74" t="n">
         <v>323</v>
@@ -7139,12 +8423,15 @@
         <v>32</v>
       </c>
       <c r="D74" t="n">
-        <v>0.909859154929577</v>
+        <v>0.91</v>
+      </c>
+      <c r="E74" t="n">
+        <v>10.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B75" t="n">
         <v>247</v>
@@ -7153,12 +8440,15 @@
         <v>42</v>
       </c>
       <c r="D75" t="n">
-        <v>0.854671280276817</v>
+        <v>0.85</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5.88</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B76" t="n">
         <v>98</v>
@@ -7167,12 +8457,15 @@
         <v>15</v>
       </c>
       <c r="D76" t="n">
-        <v>0.867256637168142</v>
+        <v>0.87</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6.53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B77" t="n">
         <v>178</v>
@@ -7181,12 +8474,15 @@
         <v>44</v>
       </c>
       <c r="D77" t="n">
-        <v>0.801801801801802</v>
+        <v>0.8</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B78" t="n">
         <v>223</v>
@@ -7195,12 +8491,15 @@
         <v>35</v>
       </c>
       <c r="D78" t="n">
-        <v>0.864341085271318</v>
+        <v>0.86</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6.37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B79" t="n">
         <v>325</v>
@@ -7209,12 +8508,15 @@
         <v>37</v>
       </c>
       <c r="D79" t="n">
-        <v>0.897790055248619</v>
+        <v>0.9</v>
+      </c>
+      <c r="E79" t="n">
+        <v>8.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B80" t="n">
         <v>198</v>
@@ -7223,12 +8525,15 @@
         <v>32</v>
       </c>
       <c r="D80" t="n">
-        <v>0.860869565217391</v>
+        <v>0.86</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6.19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B81" t="n">
         <v>149</v>
@@ -7237,12 +8542,15 @@
         <v>15</v>
       </c>
       <c r="D81" t="n">
-        <v>0.908536585365854</v>
+        <v>0.91</v>
+      </c>
+      <c r="E81" t="n">
+        <v>9.93</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B82" t="n">
         <v>334</v>
@@ -7251,12 +8559,15 @@
         <v>26</v>
       </c>
       <c r="D82" t="n">
-        <v>0.927777777777778</v>
+        <v>0.93</v>
+      </c>
+      <c r="E82" t="n">
+        <v>12.85</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B83" t="n">
         <v>218</v>
@@ -7265,12 +8576,15 @@
         <v>28</v>
       </c>
       <c r="D83" t="n">
-        <v>0.886178861788618</v>
+        <v>0.89</v>
+      </c>
+      <c r="E83" t="n">
+        <v>7.79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B84" t="n">
         <v>264</v>
@@ -7279,12 +8593,15 @@
         <v>28</v>
       </c>
       <c r="D84" t="n">
-        <v>0.904109589041096</v>
+        <v>0.9</v>
+      </c>
+      <c r="E84" t="n">
+        <v>9.43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" t="n">
         <v>127</v>
@@ -7293,12 +8610,15 @@
         <v>27</v>
       </c>
       <c r="D85" t="n">
-        <v>0.824675324675325</v>
+        <v>0.82</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B86" t="n">
         <v>406</v>
@@ -7307,12 +8627,15 @@
         <v>39</v>
       </c>
       <c r="D86" t="n">
-        <v>0.912359550561798</v>
+        <v>0.91</v>
+      </c>
+      <c r="E86" t="n">
+        <v>10.41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B87" t="n">
         <v>434</v>
@@ -7321,7 +8644,10 @@
         <v>26</v>
       </c>
       <c r="D87" t="n">
-        <v>0.943478260869565</v>
+        <v>0.94</v>
+      </c>
+      <c r="E87" t="n">
+        <v>16.69</v>
       </c>
     </row>
   </sheetData>
@@ -7337,13 +8663,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C1" t="s">
         <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -7354,7 +8683,10 @@
         <v>411445</v>
       </c>
       <c r="C2" t="n">
-        <v>0.599750447139836</v>
+        <v>0.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -7370,21 +8702,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="n">
         <v>913</v>
@@ -7393,12 +8728,15 @@
         <v>709</v>
       </c>
       <c r="D2" t="n">
-        <v>0.43711467324291</v>
+        <v>0.44</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="n">
         <v>14490</v>
@@ -7407,12 +8745,15 @@
         <v>20694</v>
       </c>
       <c r="D3" t="n">
-        <v>0.588165075034106</v>
+        <v>0.59</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="n">
         <v>900</v>
@@ -7421,12 +8762,15 @@
         <v>1435</v>
       </c>
       <c r="D4" t="n">
-        <v>0.614561027837259</v>
+        <v>0.61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="n">
         <v>1353</v>
@@ -7435,12 +8779,15 @@
         <v>2623</v>
       </c>
       <c r="D5" t="n">
-        <v>0.659708249496982</v>
+        <v>0.66</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="n">
         <v>886</v>
@@ -7449,12 +8796,15 @@
         <v>1204</v>
       </c>
       <c r="D6" t="n">
-        <v>0.576076555023923</v>
+        <v>0.58</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="n">
         <v>212</v>
@@ -7463,12 +8813,15 @@
         <v>185</v>
       </c>
       <c r="D7" t="n">
-        <v>0.465994962216625</v>
+        <v>0.47</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="n">
         <v>2303</v>
@@ -7477,12 +8830,15 @@
         <v>3781</v>
       </c>
       <c r="D8" t="n">
-        <v>0.62146614069691</v>
+        <v>0.62</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="n">
         <v>860</v>
@@ -7491,12 +8847,15 @@
         <v>808</v>
       </c>
       <c r="D9" t="n">
-        <v>0.484412470023981</v>
+        <v>0.48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="n">
         <v>1264</v>
@@ -7505,12 +8864,15 @@
         <v>2779</v>
       </c>
       <c r="D10" t="n">
-        <v>0.687360870640613</v>
+        <v>0.69</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="n">
         <v>5036</v>
@@ -7519,12 +8881,15 @@
         <v>5798</v>
       </c>
       <c r="D11" t="n">
-        <v>0.535167066642053</v>
+        <v>0.54</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="n">
         <v>1221</v>
@@ -7533,12 +8898,15 @@
         <v>1200</v>
       </c>
       <c r="D12" t="n">
-        <v>0.495662949194548</v>
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>432</v>
@@ -7547,12 +8915,15 @@
         <v>317</v>
       </c>
       <c r="D13" t="n">
-        <v>0.423230974632844</v>
+        <v>0.42</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="n">
         <v>2100</v>
@@ -7561,12 +8932,15 @@
         <v>2086</v>
       </c>
       <c r="D14" t="n">
-        <v>0.498327759197324</v>
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="n">
         <v>1779</v>
@@ -7575,12 +8949,15 @@
         <v>3799</v>
       </c>
       <c r="D15" t="n">
-        <v>0.681068483327357</v>
+        <v>0.68</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
         <v>185</v>
@@ -7589,12 +8966,15 @@
         <v>342</v>
       </c>
       <c r="D16" t="n">
-        <v>0.648956356736243</v>
+        <v>0.65</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
         <v>410</v>
@@ -7603,12 +8983,15 @@
         <v>1059</v>
       </c>
       <c r="D17" t="n">
-        <v>0.720898570456093</v>
+        <v>0.72</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="n">
         <v>232</v>
@@ -7617,12 +9000,15 @@
         <v>211</v>
       </c>
       <c r="D18" t="n">
-        <v>0.476297968397291</v>
+        <v>0.48</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="n">
         <v>2679</v>
@@ -7631,12 +9017,15 @@
         <v>2408</v>
       </c>
       <c r="D19" t="n">
-        <v>0.47336347552585</v>
+        <v>0.47</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="n">
         <v>30616</v>
@@ -7645,12 +9034,15 @@
         <v>30562</v>
       </c>
       <c r="D20" t="n">
-        <v>0.499558664879532</v>
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" t="n">
         <v>442</v>
@@ -7659,12 +9051,15 @@
         <v>654</v>
       </c>
       <c r="D21" t="n">
-        <v>0.596715328467153</v>
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" t="n">
         <v>1644</v>
@@ -7673,12 +9068,15 @@
         <v>1355</v>
       </c>
       <c r="D22" t="n">
-        <v>0.451817272424141</v>
+        <v>0.45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="n">
         <v>644</v>
@@ -7687,12 +9085,15 @@
         <v>532</v>
       </c>
       <c r="D23" t="n">
-        <v>0.452380952380952</v>
+        <v>0.45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" t="n">
         <v>697</v>
@@ -7701,12 +9102,15 @@
         <v>905</v>
       </c>
       <c r="D24" t="n">
-        <v>0.564918851435705</v>
+        <v>0.56</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="n">
         <v>901</v>
@@ -7715,12 +9119,15 @@
         <v>1156</v>
       </c>
       <c r="D25" t="n">
-        <v>0.56198347107438</v>
+        <v>0.56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" t="n">
         <v>2501</v>
@@ -7729,12 +9136,15 @@
         <v>2062</v>
       </c>
       <c r="D26" t="n">
-        <v>0.451895682664913</v>
+        <v>0.45</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" t="n">
         <v>323</v>
@@ -7743,12 +9153,15 @@
         <v>231</v>
       </c>
       <c r="D27" t="n">
-        <v>0.416967509025271</v>
+        <v>0.42</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" t="n">
         <v>85173</v>
@@ -7757,12 +9170,15 @@
         <v>153036</v>
       </c>
       <c r="D28" t="n">
-        <v>0.64244424014206</v>
+        <v>0.64</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" t="n">
         <v>493</v>
@@ -7771,12 +9187,15 @@
         <v>898</v>
       </c>
       <c r="D29" t="n">
-        <v>0.645578720345075</v>
+        <v>0.65</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" t="n">
         <v>872</v>
@@ -7785,12 +9204,15 @@
         <v>948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.520879120879121</v>
+        <v>0.52</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B31" t="n">
         <v>1309</v>
@@ -7799,12 +9221,15 @@
         <v>1341</v>
       </c>
       <c r="D31" t="n">
-        <v>0.506037735849057</v>
+        <v>0.51</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" t="n">
         <v>1973</v>
@@ -7813,12 +9238,15 @@
         <v>2406</v>
       </c>
       <c r="D32" t="n">
-        <v>0.549440511532313</v>
+        <v>0.55</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" t="n">
         <v>276</v>
@@ -7827,12 +9255,15 @@
         <v>253</v>
       </c>
       <c r="D33" t="n">
-        <v>0.478260869565217</v>
+        <v>0.48</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B34" t="n">
         <v>502</v>
@@ -7841,12 +9272,15 @@
         <v>475</v>
       </c>
       <c r="D34" t="n">
-        <v>0.48618219037871</v>
+        <v>0.49</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" t="n">
         <v>1589</v>
@@ -7855,12 +9289,15 @@
         <v>1304</v>
       </c>
       <c r="D35" t="n">
-        <v>0.450743173176633</v>
+        <v>0.45</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36" t="n">
         <v>145</v>
@@ -7869,12 +9306,15 @@
         <v>292</v>
       </c>
       <c r="D36" t="n">
-        <v>0.668192219679634</v>
+        <v>0.67</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B37" t="n">
         <v>368</v>
@@ -7883,12 +9323,15 @@
         <v>675</v>
       </c>
       <c r="D37" t="n">
-        <v>0.647171620325983</v>
+        <v>0.65</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B38" t="n">
         <v>266</v>
@@ -7897,12 +9340,15 @@
         <v>271</v>
       </c>
       <c r="D38" t="n">
-        <v>0.504655493482309</v>
+        <v>0.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B39" t="n">
         <v>467</v>
@@ -7911,12 +9357,15 @@
         <v>1189</v>
       </c>
       <c r="D39" t="n">
-        <v>0.717995169082126</v>
+        <v>0.72</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B40" t="n">
         <v>100</v>
@@ -7925,12 +9374,15 @@
         <v>145</v>
       </c>
       <c r="D40" t="n">
-        <v>0.591836734693878</v>
+        <v>0.59</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B41" t="n">
         <v>1310</v>
@@ -7939,12 +9391,15 @@
         <v>817</v>
       </c>
       <c r="D41" t="n">
-        <v>0.384109073812882</v>
+        <v>0.38</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B42" t="n">
         <v>128</v>
@@ -7953,12 +9408,15 @@
         <v>150</v>
       </c>
       <c r="D42" t="n">
-        <v>0.539568345323741</v>
+        <v>0.54</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B43" t="n">
         <v>639</v>
@@ -7967,12 +9425,15 @@
         <v>714</v>
       </c>
       <c r="D43" t="n">
-        <v>0.527716186252772</v>
+        <v>0.53</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B44" t="n">
         <v>123</v>
@@ -7981,12 +9442,15 @@
         <v>260</v>
       </c>
       <c r="D44" t="n">
-        <v>0.678851174934726</v>
+        <v>0.68</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B45" t="n">
         <v>194</v>
@@ -7995,12 +9459,15 @@
         <v>250</v>
       </c>
       <c r="D45" t="n">
-        <v>0.563063063063063</v>
+        <v>0.56</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B46" t="n">
         <v>444</v>
@@ -8009,12 +9476,15 @@
         <v>466</v>
       </c>
       <c r="D46" t="n">
-        <v>0.512087912087912</v>
+        <v>0.51</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B47" t="n">
         <v>915</v>
@@ -8023,12 +9493,15 @@
         <v>947</v>
       </c>
       <c r="D47" t="n">
-        <v>0.50859291084855</v>
+        <v>0.51</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B48" t="n">
         <v>719</v>
@@ -8037,12 +9510,15 @@
         <v>520</v>
       </c>
       <c r="D48" t="n">
-        <v>0.419693301049233</v>
+        <v>0.42</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B49" t="n">
         <v>648</v>
@@ -8051,12 +9527,15 @@
         <v>722</v>
       </c>
       <c r="D49" t="n">
-        <v>0.527007299270073</v>
+        <v>0.53</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B50" t="n">
         <v>770</v>
@@ -8065,12 +9544,15 @@
         <v>669</v>
       </c>
       <c r="D50" t="n">
-        <v>0.464906184850591</v>
+        <v>0.46</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B51" t="n">
         <v>1163</v>
@@ -8079,12 +9561,15 @@
         <v>1243</v>
       </c>
       <c r="D51" t="n">
-        <v>0.516625103906899</v>
+        <v>0.52</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B52" t="n">
         <v>198</v>
@@ -8093,12 +9578,15 @@
         <v>258</v>
       </c>
       <c r="D52" t="n">
-        <v>0.565789473684211</v>
+        <v>0.57</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B53" t="n">
         <v>1352</v>
@@ -8107,12 +9595,15 @@
         <v>2003</v>
       </c>
       <c r="D53" t="n">
-        <v>0.597019374068554</v>
+        <v>0.6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B54" t="n">
         <v>232</v>
@@ -8121,12 +9612,15 @@
         <v>445</v>
       </c>
       <c r="D54" t="n">
-        <v>0.657311669128508</v>
+        <v>0.66</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B55" t="n">
         <v>253</v>
@@ -8135,12 +9629,15 @@
         <v>294</v>
       </c>
       <c r="D55" t="n">
-        <v>0.537477148080439</v>
+        <v>0.54</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B56" t="n">
         <v>5767</v>
@@ -8149,12 +9646,15 @@
         <v>12973</v>
       </c>
       <c r="D56" t="n">
-        <v>0.692262540021345</v>
+        <v>0.69</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B57" t="n">
         <v>1702</v>
@@ -8163,12 +9663,15 @@
         <v>2192</v>
       </c>
       <c r="D57" t="n">
-        <v>0.562917308680021</v>
+        <v>0.56</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B58" t="n">
         <v>203</v>
@@ -8177,12 +9680,15 @@
         <v>336</v>
       </c>
       <c r="D58" t="n">
-        <v>0.623376623376623</v>
+        <v>0.62</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B59" t="n">
         <v>980</v>
@@ -8191,12 +9697,15 @@
         <v>1026</v>
       </c>
       <c r="D59" t="n">
-        <v>0.511465603190429</v>
+        <v>0.51</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B60" t="n">
         <v>185</v>
@@ -8205,12 +9714,15 @@
         <v>285</v>
       </c>
       <c r="D60" t="n">
-        <v>0.606382978723404</v>
+        <v>0.61</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B61" t="n">
         <v>617</v>
@@ -8219,12 +9731,15 @@
         <v>901</v>
       </c>
       <c r="D61" t="n">
-        <v>0.593544137022398</v>
+        <v>0.59</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B62" t="n">
         <v>477</v>
@@ -8233,12 +9748,15 @@
         <v>407</v>
       </c>
       <c r="D62" t="n">
-        <v>0.460407239819004</v>
+        <v>0.46</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B63" t="n">
         <v>31986</v>
@@ -8247,12 +9765,15 @@
         <v>59369</v>
       </c>
       <c r="D63" t="n">
-        <v>0.649871380876799</v>
+        <v>0.65</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B64" t="n">
         <v>97</v>
@@ -8261,12 +9782,15 @@
         <v>151</v>
       </c>
       <c r="D64" t="n">
-        <v>0.608870967741935</v>
+        <v>0.61</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.56</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B65" t="n">
         <v>359</v>
@@ -8275,12 +9799,15 @@
         <v>412</v>
       </c>
       <c r="D65" t="n">
-        <v>0.534370946822309</v>
+        <v>0.53</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B66" t="n">
         <v>374</v>
@@ -8289,12 +9816,15 @@
         <v>267</v>
       </c>
       <c r="D66" t="n">
-        <v>0.416536661466459</v>
+        <v>0.42</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B67" t="n">
         <v>3499</v>
@@ -8303,12 +9833,15 @@
         <v>3473</v>
       </c>
       <c r="D67" t="n">
-        <v>0.498135398737808</v>
+        <v>0.5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B68" t="n">
         <v>180</v>
@@ -8317,12 +9850,15 @@
         <v>415</v>
       </c>
       <c r="D68" t="n">
-        <v>0.697478991596639</v>
+        <v>0.7</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B69" t="n">
         <v>236</v>
@@ -8331,12 +9867,15 @@
         <v>355</v>
       </c>
       <c r="D69" t="n">
-        <v>0.600676818950931</v>
+        <v>0.6</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B70" t="n">
         <v>7212</v>
@@ -8345,12 +9884,15 @@
         <v>6936</v>
       </c>
       <c r="D70" t="n">
-        <v>0.490245971162002</v>
+        <v>0.49</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B71" t="n">
         <v>2347</v>
@@ -8359,12 +9901,15 @@
         <v>2954</v>
       </c>
       <c r="D71" t="n">
-        <v>0.557253348424826</v>
+        <v>0.56</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B72" t="n">
         <v>602</v>
@@ -8373,12 +9918,15 @@
         <v>459</v>
       </c>
       <c r="D72" t="n">
-        <v>0.432610744580584</v>
+        <v>0.43</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B73" t="n">
         <v>8384</v>
@@ -8387,12 +9935,15 @@
         <v>19372</v>
       </c>
       <c r="D73" t="n">
-        <v>0.697939184320507</v>
+        <v>0.7</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B74" t="n">
         <v>4628</v>
@@ -8401,12 +9952,15 @@
         <v>6372</v>
       </c>
       <c r="D74" t="n">
-        <v>0.579272727272727</v>
+        <v>0.58</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.38</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B75" t="n">
         <v>1126</v>
@@ -8415,12 +9969,15 @@
         <v>1248</v>
       </c>
       <c r="D75" t="n">
-        <v>0.525695029486099</v>
+        <v>0.53</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B76" t="n">
         <v>288</v>
@@ -8429,12 +9986,15 @@
         <v>403</v>
       </c>
       <c r="D76" t="n">
-        <v>0.583212735166425</v>
+        <v>0.58</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B77" t="n">
         <v>409</v>
@@ -8443,12 +10003,15 @@
         <v>263</v>
       </c>
       <c r="D77" t="n">
-        <v>0.391369047619048</v>
+        <v>0.39</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B78" t="n">
         <v>623</v>
@@ -8457,12 +10020,15 @@
         <v>494</v>
       </c>
       <c r="D78" t="n">
-        <v>0.442256042972247</v>
+        <v>0.44</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B79" t="n">
         <v>136</v>
@@ -8471,12 +10037,15 @@
         <v>56</v>
       </c>
       <c r="D79" t="n">
-        <v>0.291666666666667</v>
+        <v>0.29</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B80" t="n">
         <v>990</v>
@@ -8485,12 +10054,15 @@
         <v>765</v>
       </c>
       <c r="D80" t="n">
-        <v>0.435897435897436</v>
+        <v>0.44</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B81" t="n">
         <v>399</v>
@@ -8499,12 +10071,15 @@
         <v>358</v>
       </c>
       <c r="D81" t="n">
-        <v>0.472919418758256</v>
+        <v>0.47</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B82" t="n">
         <v>504</v>
@@ -8513,12 +10088,15 @@
         <v>540</v>
       </c>
       <c r="D82" t="n">
-        <v>0.517241379310345</v>
+        <v>0.52</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B83" t="n">
         <v>16163</v>
@@ -8527,12 +10105,15 @@
         <v>18230</v>
       </c>
       <c r="D83" t="n">
-        <v>0.530049719419649</v>
+        <v>0.53</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B84" t="n">
         <v>322</v>
@@ -8541,12 +10122,15 @@
         <v>296</v>
       </c>
       <c r="D84" t="n">
-        <v>0.478964401294498</v>
+        <v>0.48</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B85" t="n">
         <v>127</v>
@@ -8555,12 +10139,15 @@
         <v>155</v>
       </c>
       <c r="D85" t="n">
-        <v>0.549645390070922</v>
+        <v>0.55</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B86" t="n">
         <v>1483</v>
@@ -8569,12 +10156,15 @@
         <v>2951</v>
       </c>
       <c r="D86" t="n">
-        <v>0.66553901668922</v>
+        <v>0.67</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B87" t="n">
         <v>4222</v>
@@ -8583,12 +10173,15 @@
         <v>4848</v>
       </c>
       <c r="D87" t="n">
-        <v>0.534509371554576</v>
+        <v>0.53</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B88" t="n">
         <v>311</v>
@@ -8597,7 +10190,10 @@
         <v>297</v>
       </c>
       <c r="D88" t="n">
-        <v>0.488486842105263</v>
+        <v>0.49</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-1.05</v>
       </c>
     </row>
   </sheetData>
